--- a/MSMS_peaklist_example.xlsx
+++ b/MSMS_peaklist_example.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20385"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kslynn_2\Google 雲端硬碟\research\Metabolomics\FSM_matlab\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Google 雲端硬碟\research\Metabolomics\FSM_matlab\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E660FB2-2C28-44E6-8D2B-C59AC3039726}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MSMS_peaklist" sheetId="2" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="360">
   <si>
     <t>ms2_peak</t>
   </si>
@@ -321,6 +322,309 @@
     <t>107.0358;12.79;134.0467;100;266.089;15.9287</t>
   </si>
   <si>
+    <t>ms2_peak</t>
+  </si>
+  <si>
+    <t>112.0536;1;117.0582;0.25826;228.0984;0.5045</t>
+  </si>
+  <si>
+    <t>66.0362;0.15516;93.0472;1;135.0583;0.15215;209.9796;0.12012;226.0144;0.14214;226.0828;0.24024</t>
+  </si>
+  <si>
+    <t>66.0362;14.04;93.0472;90.66;135.0583;13.81;209.9796;10.85;226.0144;12.92;226.0828;21.75</t>
+  </si>
+  <si>
+    <t>112.0536;100;117.0582;25.8384;228.0984;50.4916</t>
+  </si>
+  <si>
+    <t>45.1994;212;45.3655;184;45.3856;140;45.8184;172;46.0208;160;46.2546;144;46.443;156;47.2687;204;47.9168;104;48.2937;88;48.3352;116;48.9864;152;49.3646;180;49.4668;64;49.6265;184;49.6587;120;49.92;164;50.0677;180;50.11;204;50.148;236;50.2623;256;50.299;144;50.3555;164;51.3447;172;52.263;232;52.3955;76;53.4103;156;53.4278;168;53.4409;140;54.1782;104;55.6294;228;56.6615;132;56.7244;104;57.386;188;57.9316;184;57.9603;84;58.1181;192;58.2942;84;58.3702;168;58.6321;180;59.0657;40;59.4334;136;59.6484;224;59.833;104;60.268;140;60.3561;212;60.6565;160;60.7697;180;62.9361;176;64.0941;72;64.311;168;64.5682;180;64.6674;156;64.7539;148;64.8067;164;65.1613;160;65.4761;216;65.6184;172;66.4141;56;66.6138;244;66.7552;104;67.6804;44;67.7771;100;67.7918;72;68.2301;88;69.048;204;69.1936;168;69.3063;60;69.5932;164;69.648;128;71.7433;188;71.8664;52;72.3582;40;72.4056;72;72.7006;80;72.9418;184;73.9157;164;74.1092;136;74.1212;92;74.2035;136;74.2378;164;74.43;152;75.2807;148;75.3826;168;75.7477;84;75.8465;204;76.1692;156;76.5048;164;77.4198;96;78.0533;80;78.852;120;79.9053;152;80.3043;124;80.3168;196;80.8206;208;80.9298;176;80.9674;80;81.2238;160;81.4302;164;81.5739;148;81.6602;164;81.7664;108;81.9951;192;82.6525;200;82.667;200;82.7303;180;82.7764;164;83.1744;172;84.2324;140;84.5543;180;84.6971;180;84.7447;120;84.9427;152;85.4479;180;85.9399;184;86.1079;156;86.2113;204;86.6017;72;86.8019;232;87.2401;180;87.4652;80;87.8509;240;87.8808;160;87.9685;172;88.0021;204;89.3008;184;89.4287;44;89.8263;200;89.9679;76;90.0868;160;90.1946;148;90.5465;36;90.7398;208;91.0535;376;91.07;140;91.1251;124;91.4864;140;91.515;164;92.3451;172;92.5327;128;92.9323;196;93.0697;224;93.379;100;93.7313;220;93.8315;144;94.0383;192;95.054;144;95.0856;300;95.1044;156;95.1219;128;95.2753;140;95.9531;196;96.5286;148;96.6401;160;96.8966;136;97.024;228;97.0644;3204;97.1103;192;97.1711;60;97.3203;180;97.4303;132;97.7842;148;97.8236;44;97.8846;168;98.0672;372;98.1014;192;98.4012;148;98.8341;164;98.8776;156;99.0301;140;99.5239;140;100.0787;156;100.7109;164;101.8587;172;102.1723;188;102.2648;176;103.0534;172;103.114;136;103.2656;144;104.1555;64;104.3831;68;104.4258;168;104.5479;240;105.0699;1112;105.2532;232;105.3513;76;105.572;156;106.0408;168;106.0818;132;106.4327;164;106.5559;184;106.8108;180;106.994;116;107.0487;596;107.0702;124;107.0874;412;107.5444;200;108.0556;196;108.1645;124;108.2784;164;108.774;156;109.017;232;109.0419;180;109.0642;7720;109.1007;380;109.172;76;109.2395;56;109.3185;64;109.4788;80;109.7852;68;110.0675;740;110.1045;168;110.1337;96;110.6691;172;110.7864;72;111.0233;100;111.0421;200;111.0798;164;112.9801;56;113.0605;136;113.5775;144;113.7367;84;113.8704;188;114.0043;52;114.0893;176;115.0492;136;116.0597;180;116.1372;148;116.2574;44;116.8913;224;117.0677;636;117.6716;220;117.8682;116;118.0711;216;119.051;144;119.0854;1132;119.1226;36;119.1704;72;119.821;192;120.0879;212;120.2375;184;120.5629;124;120.6175;120;120.8537;92;121.0636;1284;121.1038;196;121.6691;68;122.1438;132;122.659;180;122.8531;136;123.0539;180;123.0794;1672;124.0943;188;124.1316;112;125.0612;192;125.0914;152;126.0572;212;126.1957;140;126.659;192;127.065;184;127.5701;176;128.0615;348;128.1755;144;128.6447;220;128.8253;156;129.0695;396;129.3364;140;129.5493;56;129.8757;104;130.0368;164;130.072;316;130.1571;52;131.0858;1396;131.1103;172;131.9846;156;132.0914;388;132.1539;200;132.5019;108;133.0613;336;133.0982;1192;133.4521;132;133.528;76;133.6844;172;134.0668;164;134.1059;148;134.2604;144;134.759;200;135.0808;240;135.0971;176;135.1141;184;135.4484;184;135.6825;208;135.8518;188;135.9933;256;137.0985;236;138.9149;32;139.0298;108;139.0768;184;139.1613;36;139.4455;312;139.5114;124;141.0671;736;142.078;432;142.1687;52;143.0267;208;143.086;936;143.5938;180;144.064;152;144.0886;324;144.8032;100;145.0617;200;145.1007;2036;145.213;44;145.5274;76;146.1047;424;146.1403;64;146.3064;28;146.4099;228;146.6725;180;146.9402;96;147.0762;140;147.1174;820;147.6843;152;147.9456;156;148.0901;184;148.1208;160;148.3211;52;148.503;192;148.9302;216;149.0565;136;149.0954;272;149.1273;436;149.4091;56;149.7426;44;150.0886;100;151.0704;148;151.1083;168;151.3225;124;152.0626;140;152.2568;184;152.9207;204;153.024;212;153.0711;116;153.2383;164;153.4355;84;154.0791;140;154.097;220;155.0854;736;155.1761;92;156.0918;128;157.0537;32;157.0992;996;157.2159;64;158.1065;552;158.2733;40;159.0797;320;159.1177;976;160.0184;152;160.0637;216;160.0914;120;160.1231;308;160.714;144;161.017;96;161.0963;752;161.1293;684;161.6167;176;162.1073;108;162.1251;80;162.1428;116;162.2112;100;163.1088;540;163.5957;64;164.0314;72;164.1053;92;165.0695;284;165.0878;196;165.311;88;166.0719;176;166.2618;76;167.0785;244;167.0835;196;167.7794;160;168.092;296;169.0986;988;170.0662;228;170.0844;148;170.1106;132;171.08;568;171.1148;716;171.1607;56;171.7784;48;172.0799;140;172.1183;164;173.0972;168;173.1288;972;173.4546;40;174.1003;152;174.1368;112;174.5126;48;174.8441;52;174.902;52;175.1099;480;175.1434;280;175.4605;60;176.0806;128;176.1202;136;176.6515;80;177.0671;136;177.1272;500;177.1545;176;178.0723;172;178.16;216;178.556;48;179.0812;200;179.1078;112;179.2349;132;180.1447;36;181.0946;488;181.7887;180;182.1021;364;182.5974;140;183.1202;484;184.076;184;184.1204;376;184.7175;52;185.093;144;185.1307;832;185.1559;116;185.4323;100;185.9178;52;186.173;56;186.2006;252;186.3332;156;186.3821;64;186.8961;240;187.1082;452;187.1467;332;188.1089;100;188.158;176;189.1327;204;189.1606;180;189.5914;164;191.0797;204;191.1044;180;191.1406;344;191.7571;120;192.0935;180;192.1424;144;192.4412;128;193.1048;416;193.1985;84;193.9406;140;194.1051;156;194.9064;180;195.1131;352;196.1115;152;196.1505;156;196.315;132;196.7056;136;197.0952;132;197.1259;448;198.1067;256;198.1346;184;199.0266;164;199.1052;344;199.1456;320;200.1201;172;200.1409;164;201.0873;176;201.1238;300;201.1604;120;201.3414;76;202.0538;40;202.1304;244;203.0906;172;203.1388;356;203.3772;124;204.1073;168;204.1414;152;205.1138;136;205.4802;208;206.1081;144;206.8605;172;207.1135;204;207.4908;164;207.8694;84;208.122;184;208.668;212;208.8031;108;209.0908;128;209.1297;772;209.6611;116;210.1388;440;211.1018;320;211.1495;324;211.8107;184;212.1532;160;213.1286;364;213.1543;136;213.3139;128;213.7822;40;214.0704;32;214.1607;192;214.4724;176;214.6299;160;215.1062;160;215.14;216;215.1753;176;216.5499;188;216.755;88;217.098;192;217.1214;128;217.16;172;219.1332;304;220.1278;128;221.1254;116;221.158;72;221.2793;108;222.1468;152;223.1366;228;223.1458;532;223.3775;136;225.1185;180;225.1595;336;225.5395;44;226.1758;136;226.9825;32;227.1415;352;227.2045;116;228.1421;268;228.1806;272;228.7943;176;229.1226;208;229.1556;348;230.0967;124;230.1571;176;231.1758;144;231.2061;124;232.4243;104;233.1314;168;233.2018;148;234.1478;164;235.1465;492;236.1594;140;236.343;92;236.7501;128;237.1361;140;237.16;464;238.1601;144;238.5942;36;238.7018;72;239.1756;132;239.3327;64;240.1463;200;241.163;160;241.1961;140;242.2234;44;242.3567;48;243.0202;140;243.1722;632;243.5169;60;243.6349;128;243.7157;88;244.1758;188;244.2069;144;245.1463;156;245.1795;124;245.6991;72;246.1359;168;246.1954;140;246.2172;92;247.6998;132;247.9818;128;248.1636;160;248.4647;40;249.1607;196;250.1681;196;251.0819;156;251.1418;224;251.1836;316;252.1483;172;252.1877;116;252.9334;124;253.1594;260;253.195;1112;253.5194;56;254.1627;424;254.203;132;255.1677;484;255.1973;184;256.1789;180;258.1706;200;259.0316;148;259.1629;240;259.4802;132;263.1777;240;264.1597;104;265.1812;112;265.2094;172;265.465;104;266.0425;92;266.1562;152;266.2049;264;267.1735;104;267.1963;84;267.9516;44;268.1406;152;269.1871;308;270.1968;284;271.1633;216;271.1996;656;271.6852;60;272.2005;188;273.2392;156;275.181;348;278.1733;192;278.6316;136;280.1454;232;281.1927;276;282.1894;168;283.2034;488;284.174;48;284.2009;40;284.7178;108;287.2051;72;288.1943;96;289.1039;156;289.2122;100;292.168;204;293.1805;320;294.1932;156;294.363;136;295.2071;88;299.1945;440;300.5591;44;301.1805;116;301.6436;48;302.2142;176;303.8565;44;305.2181;128;305.8304;104;311.195;488;312.1946;348;315.1875;100;315.3607;68;317.2226;148;319.218;144;328.0909;144;329.2101;308;330.2219;220;331.9743;40;346.1274;60;347.2194;500;347.2726;108;348.2205;208;349.2263;252;350.3579;72;385.2639;104;393.8079;116;396.9066;152;426.0975;56;435.3004;52;438.2413;168;521.6012;40;552.7031;92;607.172;176;728.4968;72;750.4655;84;775.6513;136;858.8341;180;870.0933;144;882.75;228;894.9026;124;895.927;172;902.8392;104;918.4252;200;947.7598;180;966.12;164;983.3265;156;985.7496;212;990.8868;208;991.0372;148;1022.5057;168;1029.2249;180;1030.6429;164;1031.5824;160;1041.3223;160;1044.7742;152;1050.6046;64;1061.3217;184;1072.3734;208;1073.8927;252;1080.3204;192;1082.8274;164;1083.6069;180;1094.5697;180;1103.3849;144;1112.4811;168;1117.286;72;1119.6824;116;1120.4352;228;1126.4794;216;1130.0829;68;1134.3691;148;1136.6361;64;1139.3756;108;1143.8275;188;1146.9801;160;1149.3945;64;1151.8251;168;1155.0765;116;1158.6781;160;1161.7966;108;1169.244;184;1170.5784;200;1175.0363;176;1189.8882;176;1190.3551;112;1191.7565;152;1193.9149;52;1196.4196;132;1201.8853;152;1202.5271;136;1203.7214;164;1221.2559;60;1223.1834;52;1223.7959;56;1224.8545;208;1228.1935;156;1229.3936;64;1246.6635;160;1246.9586;200;1250.792;168;1252.4398;208;1254.4904;80;1258.0388;148;1263.3816;88;1269.2852;168;1271.3104;148;1271.5944;52;1272;164;1273.6677;168;1285.0726;172;1290.9158;188;1294.8949;108;1295.604;248;1297.5607;176;1300.3224;148;1302.3472;84;1304.3879;360;1308.611;104;1310.9808;192;1313.692;140;1317.6699;172;1318.4576;152;1324.7238;176;1327.1082;148;1329.8577;176;1334.0781;180;1338.4363;148;1345.5746;160;1345.6694;228;1345.8228;160;1352.8124;104;1353.7788;172;1358.4625;72;1361.3324;172;1362.4268;228;1362.5443;184;1362.8529;140;1371.0654;148;1374.871;216;1377.0927;188;1381.7579;116;1390.7841;236;1393.2719;148;1395.1149;128;1396.9741;172;1399.2664;208;1403.327;124;1405.1842;132;1405.7214;72;1407.0649;152;1408.6407;160;1409.6121;140;1412.1838;216;1416.2708;196;1420.4034;248;1424.6199;64;1426.4083;188;1431.9388;180;1434.6666;136;1439.0652;160;1443.3873;200;1443.4706;176;1447.0269;120;1450.2996;148;1454.2209;156;1461.4102;176;1464.2877;196;1475.4364;144;1476.4686;172;1479.3228;124;1479.3993;184;1482.1183;240;1482.3634;148;1484.7554;216;1486.3357;184;1488.4082;56;1498.2611;176;1501.113;208;1501.4908;164;1503.4274;72;1504.1066;200</t>
+  </si>
+  <si>
+    <t>45.0106;100;45.3142;52;45.333;48;45.3585;180;45.7507;184;45.9219;216;46.5505;228;46.9868;240;47.0169;188;47.081;216;47.4395;100;47.9518;184;48.0143;268;48.6037;108;48.6842;80;49.1031;92;49.1869;220;49.3279;184;49.846;204;49.9506;200;50.4668;248;50.4908;44;50.8621;188;50.9318;112;50.9976;244;51.3074;212;51.7392;260;51.7933;188;52.1951;184;52.7199;92;53.15;72;53.381;180;53.445;72;53.8941;108;53.9058;96;54.1003;208;54.5213;196;54.9012;104;55.9488;64;56.0441;244;56.4487;184;56.519;184;56.823;204;56.9403;208;57.0379;236;57.1793;48;57.8384;196;57.8486;196;58.1224;264;58.4947;88;58.6029;200;58.9691;240;59.1037;200;59.7466;208;59.8574;180;59.8883;192;60.0146;108;60.3621;188;60.7726;204;60.8704;228;61.0429;88;61.3527;104;61.5774;192;62.0438;224;62.6662;80;62.928;104;62.9653;80;63.0007;224;63.105;212;63.2363;68;63.7835;180;63.8455;220;64.4753;64;64.5137;104;64.5568;208;64.8498;200;64.9605;288;65.0054;72;65.068;288;65.2778;204;65.6054;112;65.6296;184;65.8539;188;66.3102;180;66.4229;240;66.8233;56;66.9107;276;67.0872;232;67.2225;108;67.3254;104;67.4431;48;67.6312;180;67.8402;224;67.8802;84;68.2558;200;68.729;68;70.0022;188;70.2806;100;70.844;220;70.8658;60;71.1375;212;71.2786;100;72.3463;112;73.3673;64;73.3929;208;73.6335;32;74.0868;188;74.6894;104;74.7238;204;75.0821;224;75.1115;48;75.5918;72;75.8204;200;76.0233;208;76.216;104;76.2943;84;76.557;100;76.9302;216;76.993;192;77.0175;60;77.4881;220;77.5214;180;78.0181;184;78.3543;188;79.004;112;79.0854;204;79.0978;192;79.1668;88;79.3742;92;79.4079;100;79.4877;196;80.5149;40;81.4625;72;81.5991;220;81.8276;84;81.8564;216;82.0059;104;83.0366;204;83.4015;108;83.4542;72;83.5163;200;83.6016;184;83.8183;180;84.0517;212;84.8309;192;85.0914;60;85.3888;208;85.47;192;85.6744;76;85.9473;72;86.1578;184;86.4388;84;86.6518;100;86.6833;208;86.9782;220;87.1305;72;87.5546;284;88.6794;112;88.7469;180;89.0389;632;89.0809;44;89.604;180;90.0442;244;90.3422;224;90.5826;208;90.7154;184;90.7911;220;91.0537;3160;91.1111;180;91.2069;180;91.3743;184;91.4466;44;91.6561;196;91.7018;64;92.0567;772;92.0765;188;92.3912;228;92.6381;236;92.9603;196;93.0519;280;93.2253;232;93.5195;216;94.237;180;94.5444;336;94.8718;40;95.0827;200;95.2871;32;95.3007;96;95.5905;180;95.9489;80;96.1576;212;96.7225;268;96.7597;204;97.3735;64;97.4972;100;97.5818;188;97.9892;84;98.0601;228;98.2139;184;98.7631;224;98.9977;460;99.7248;60;100.2622;212;100.294;184;100.4616;104;100.6751;216;100.9955;288;101.2131;212;101.2711;180;101.3172;44;101.4575;56;101.6982;180;102.0424;472;102.2309;260;102.4;180;102.6539;116;103.0526;2596;103.2295;76;103.3589;204;104.0568;492;104.4938;188;104.6458;72;104.7253;204;104.821;188;105.067;1168;105.2024;48;105.5886;180;106.1415;220;106.5706;180;106.6312;192;106.8235;188;107.0169;196;107.0478;1612;107.1037;216;107.1508;28;107.2662;92;107.5303;268;107.6149;68;107.8918;184;108.052;196;108.7888;204;109.1088;68;109.8815;108;109.9983;40;110.0351;204;110.4936;36;110.9984;92;111.0446;104;111.2103;200;111.2922;108;111.6852;72;111.7041;212;111.7757;208;111.8557;100;111.9336;180;112.0557;112;112.1674;72;112.5634;208;113.3468;184;113.7052;188;114.0454;224;114.079;84;114.1662;80;114.7902;108;115.0519;1016;115.115;268;115.1552;184;115.6277;88;115.6448;228;116.0545;216;116.3307;280;116.7767;116;117.0329;400;117.0691;752;117.2729;116;117.8556;64;118.0388;1104;118.2644;116;118.4029;88;119.0445;248;119.6646;68;119.865;116;119.8825;220;120.0547;192;120.0795;6964;120.1376;32;120.3274;56;120.712;40;121.0286;200;121.0825;492;121.1016;236;121.2309;60;121.4479;200;121.6718;64;121.7398;188;122.0594;112;122.4282;184;122.8139;180;123.044;400;123.4655;180;124.365;60;124.5626;96;124.6337;188;124.8783;212;124.9739;196;125.0142;15208;125.0766;60;125.2144;76;125.3688;68;125.4885;100;125.5518;72;125.6803;216;125.7986;76;125.9281;224;126.0179;1512;126.1493;236;126.1851;96;126.2075;48;126.2812;184;126.4021;100;126.5509;112;126.7111;48;126.7335;56;126.761;200;126.85;52;126.9756;88;127.0108;3256;127.0552;544;127.0877;52;127.173;256;127.1963;116;127.2165;68;127.5599;236;128.0132;444;128.0619;1804;128.2189;72;128.3519;40;128.6228;64;128.6768;184;128.7875;56;129.0074;376;129.0325;376;129.0693;1716;129.1492;72;129.5272;188;129.5702;36;129.611;36;129.6835;40;129.7765;100;129.8763;92;129.9262;48;130.0137;104;130.0641;432;130.0793;228;130.1145;188;130.2667;56;130.294;52;130.5099;72;130.7283;68;130.952;196;131.0197;200;131.0483;2304;131.3959;216;131.558;184;131.7726;68;131.8892;68;132.0495;340;132.2048;204;132.2781;100;132.4109;104;132.6171;48;133.9291;96;134.7804;204;135.0186;180;135.0404;1856;135.0642;312;135.6391;204;135.7156;104;135.8478;108;136.0225;240;136.051;4296;136.2309;196;136.3168;204;136.6563;76;136.8658;80;137.0139;380;137.0543;560;137.6587;180;137.9975;356;138.1518;204;138.9168;268;139.0026;368;139.1846;108;139.2982;184;140.018;352;140.2489;104;140.5343;100;140.9333;244;141.0085;424;141.0671;196;141.0828;236;141.1295;220;141.6383;36;142.0428;284;142.0705;280;142.338;76;142.4401;112;142.4662;228;142.987;200;143.0257;320;143.049;196;143.2608;208;143.2775;196;143.3109;72;143.5802;180;144.4736;192;144.4904;72;145.0445;244;145.6459;192;146.0626;228;147.0415;1784;147.0907;52;147.1462;84;147.2162;60;147.4022;64;147.511;80;148.0503;512;148.0707;412;149.0143;3460;149.047;380;149.106;80;149.1837;64;149.3759;52;150.0179;380;150.0605;232;150.1041;112;150.3432;60;150.8537;80;150.9368;60;151.0099;832;151.0773;80;151.25;236;152.0607;564;152.1718;224;152.6509;196;152.6706;100;152.9437;52;153.009;4300;153.0661;476;153.2959;196;153.5913;68;154.0132;60;154.0762;316;154.1669;200;154.35;40;155.0056;840;155.0578;352;156.5711;52;157.004;1728;157.1045;48;157.4015;36;157.5789;192;157.8113;204;157.8413;200;158.0073;352;158.0579;264;158.5222;88;158.6526;32;159.0016;1092;159.0409;1024;159.1217;64;159.1694;108;159.4106;80;159.6067;192;159.662;92;160.05;3760;160.2939;116;161.0578;364;161.1645;32;161.3186;108;161.3515;188;161.4729;188;161.9234;60;162.0273;192;162.052;424;162.8517;332;163.0639;540;163.1389;28;163.4034;188;163.5001;204;163.5612;96;163.882;112;164.0045;292;164.0744;372;164.2568;40;164.6988;212;165.0685;2844;165.2788;44;165.5066;76;165.8089;180;165.8525;44;166.0753;1304;166.1884;188;166.3578;56;166.4323;220;166.5324;256;166.5581;48;166.8202;68;167.0818;500;167.4009;216;167.6877;116;168.0178;192;168.0598;200;168.3172;60;168.7823;40;169.0016;428;169.0281;116;169.0616;300;169.1031;192;169.4087;56;170.314;100;170.3504;104;170.6181;204;171.0198;17628;171.0534;364;171.0988;52;171.2921;36;171.5761;56;171.6335;224;171.6778;84;171.8526;52;171.9152;212;172.0219;984;172.2756;72;172.3252;256;172.3932;36;172.4297;96;172.5578;116;172.5874;76;172.8508;44;173.0164;3292;173.0489;252;173.1938;52;173.3588;56;173.4873;116;174.017;540;174.5822;60;174.7348;188;176.0631;756;176.3804;48;176.4438;80;176.5496;48;176.7063;180;176.8989;100;177.0075;2008;177.0736;892;177.2988;184;177.5348;112;177.7576;52;178.0757;1020;178.2622;188;178.3924;80;178.818;224;179.0043;752;179.0846;1916;179.4014;40;179.4627;64;179.5881;88;179.8149;80;179.995;236;180.0899;1196;180.1353;72;181.0061;544;181.0634;292;181.0991;700;181.2275;72;181.3254;212;181.4735;76;181.621;76;182.0095;572;182.038;200;182.0663;380;182.1137;204;182.7951;52;182.8193;184;183.0092;476;183.081;244;184.0169;280;184.5863;84;185.3822;188;185.6858;56;185.7889;112;186.2015;40;187.8019;60;188.0202;108;189.0658;400;189.4174;64;190.0758;812;190.2099;36;190.5834;92;191.0837;5608;191.1582;220;191.6152;80;191.8362;228;191.8853;80;192.0287;396;192.092;4460;192.1703;96;192.2715;100;192.3985;104;192.4786;108;192.5228;36;192.8267;76;193.0668;196;193.0941;808;193.2221;116;193.3356;64;193.5016;108;193.5238;44;193.5543;68;194.0031;108;194.069;948;194.5691;112;195.0177;2216;195.0748;300;195.2749;108;195.4057;44;196.0203;184;196.0851;436;196.2942;192;196.3946;84;196.4839;180;196.5536;64;197.0192;968;197.0919;300;197.7974;76;198.0298;2844;198.0985;192;198.4025;28;199.0323;904;199.4243;108;199.6633;48;199.9137;112;200.0305;796;200.4882;200;200.515;112;201.03;352;201.069;380;201.4645;188;202.0739;616;202.1077;464;202.1516;40;202.6131;36;203.0842;364;204.0492;228;204.0963;316;204.7521;112;205.0622;500;205.3991;196;205.6902;48;206.0672;272;207.0737;368;207.6961;56;208.0842;1484;209.0918;912;209.1184;360;210.0634;576;210.1051;368;210.6756;248;211.0714;740;211.3493;72;211.6879;56;212.0377;580;212.0818;224;212.1197;68;213.0379;196;213.724;60;213.816;240;214.038;364;214.7483;56;215.0633;248;216.1229;188;216.4287;48;218.0693;360;218.1774;68;218.248;72;218.6304;80;219.0799;1452;219.1222;200;219.2459;64;219.7738;180;220.0873;2728;221.0504;316;221.0905;1192;221.4382;96;221.4678;92;222.0962;64;222.2089;72;222.7344;60;223.0732;4492;223.2248;76;223.3259;72;223.5104;76;223.7128;48;223.7336;112;223.7723;80;224.0165;72;224.0777;1460;224.1064;216;224.2788;44;224.3175;48;225.0847;688;225.5683;96;226.0964;1224;226.1315;196;226.3043;104;226.3792;40;226.4227;76;226.5349;60;227.0595;680;227.0936;352;227.1284;116;227.4075;104;227.4855;84;229.0773;184;230.0837;116;231.0932;116;234.4853;116;235.0399;204;236.1016;268;237.0882;2476;237.4142;60;237.7026;108;238.097;4620;238.1539;104;238.2399;76;238.2921;40;238.3136;52;238.5288;72;238.6579;48;238.7624;88;239.1001;916;239.147;100;240.0338;296;240.1037;308;240.1669;96;240.8707;92;241.0376;104;241.0808;60;241.7983;112;243.0457;104;244.0275;332;244.8098;72;244.9406;28;245.7606;36;246.0148;240;246.0428;92;250.1704;64;255.0584;528;255.1215;112;255.6368;56;256.0612;344;256.1112;100;256.2418;116;257.0294;196;257.0606;360;257.7894;96;257.8182;72;258.0454;1104;258.1411;64;258.938;84;259.0821;76;260.0415;292;260.0762;60;260.4872;80;261.0602;108;263.8679;116;268.0845;88;268.7889;92;272.6927;80;273.0674;704;273.1794;44;274.9422;180;275.064;292;276.0357;108;276.5386;20;277.9836;96;281.015;76;285.8301;184;289.7266;96;290.0906;1704;290.2044;60;290.9729;40;292.0872;852;292.2765;32;292.61;68;293.7176;32;294.069;80;299.2146;88;315.0637;108;323.4423;44;326.4597;92;328.8448;64;334.1356;52;345.7389;104;346.7796;112;347.3506;96;369.0194;88;380.8121;112;383.2318;48;415.8038;108;440.9175;100;447.8531;116;448.4051;52;452.7018;104;455.6583;100;505.0942;104;511.4527;96;576.7516;60;626.369;48;633.0518;64;642.3655;72;652.9875;36;653.0893;64;677.878;52;708.3155;20;774.7318;56;823.8854;36;837.6711;40;840.9868;48;874.5214;60;883.2485;64;887.3347;196;907.1821;180;918.4092;228;923.0657;236;929.9785;76;933.0948;196;947.7377;188;963.7114;232;985.8525;44;992.8957;232;993.1779;116;1000.5053;228;1002.9495;188;1004.8478;100;1018.8399;184;1021.0012;268;1021.7836;240;1021.8345;80;1028.7303;112;1034.74;92;1034.9896;180;1037.1039;200;1037.4821;100;1041.39;104;1044.7006;180;1050.6018;52;1064.1091;188;1066.0448;184;1074.6925;92;1079.3892;60;1094.2184;64;1096.0364;252;1129.8267;112;1136.3993;204;1137.4261;76;1145.0242;196;1154.0941;92;1154.3375;184;1154.9056;180;1155.3791;92;1155.7445;204;1156.0829;52;1157.1592;208;1161.0217;32;1164.8296;52;1178.804;100;1181.067;192;1182.0111;228;1186.5044;204;1195.8195;44;1196.9761;188;1199.7872;208;1204.8876;232;1206.4702;184;1210.3103;64;1210.5526;248;1219.4608;224;1219.7528;188;1223.1266;32;1225.6268;76;1232.6678;200;1236.1154;192;1240.3657;192;1245.1732;220;1246.0935;96;1247.7834;116;1249.1235;204;1250.193;204;1250.552;60;1251.2771;44;1251.7347;52;1254.7928;104;1258.2924;108;1260.1217;204;1260.5951;76;1261.5988;252;1261.8392;116;1265.1503;108;1269.1605;192;1275.9342;216;1281.949;36;1284.6299;236;1286.0714;204;1287.1066;52;1293.0546;116;1297.7611;180;1297.9619;96;1300.351;192;1303.8199;276;1306.8618;200;1308.2076;224;1310.5629;232;1313.5693;264;1315.6116;204;1318.0457;180;1319.7227;208;1323.145;184;1323.8691;188;1326.811;112;1326.9125;192;1330.1337;32;1330.3949;68;1335.4817;180;1336.5076;104;1349.0963;108;1350.12;96;1350.8003;84;1358.6753;228;1368.856;180;1370.9113;180;1372.2823;112;1372.5773;68;1374.9159;60;1376.6508;216;1376.9019;112;1387.239;204;1389.7607;224;1393.5029;188;1393.9116;216;1397.28;244;1397.6967;268;1400.0565;108;1400.6151;204;1401.457;180;1401.554;184;1403.5963;116;1408.0964;188;1411.3848;220;1413.2024;196;1414.4896;32;1417.3051;224;1417.538;116;1418.6473;220;1419.6295;116;1422.3531;188;1425.162;192;1430.3363;92;1436.7344;260;1439.4592;236;1439.6556;192;1442.5117;180;1443.1846;180;1444.2737;56;1451.2714;240;1455.984;180;1456.4852;248;1458.0201;108;1461.6553;108;1464.4036;328;1466.9944;56;1469.9156;108;1470.488;180;1472.1906;204;1474.8418;240;1477.0867;228;1477.2277;236;1477.6561;112;1478.406;204;1478.6204;184;1479.4547;208;1487.7651;220;1488.5177;48;1489.8157;208;1491.7985;92;1495.7141;196;1496.0759;196;1502.3491;220;1503.1979;108</t>
+  </si>
+  <si>
+    <t>65.04;0.12312;92.0507;0.088088;120.0459;0.065065;138.0564;0.077077;148.0398;1;166.0498;0.78679;184.061;0.26126</t>
+  </si>
+  <si>
+    <t>65.0396;0.88288;92.0497;0.42843;110.0609;0.11812;120.045;0.24625;122.0239;0.13514;148.0396;1</t>
+  </si>
+  <si>
+    <t>108.0458;0.72573;138.0558;1;182.0454;0.48649</t>
+  </si>
+  <si>
+    <t>108.0458;72.5467;138.0558;100;182.0454;48.6755</t>
+  </si>
+  <si>
+    <t>65.04;12.2875;92.0507;8.8038;120.0459;6.4918;138.0564;7.667;148.0398;100;166.0498;78.6289;184.061;26.1035</t>
+  </si>
+  <si>
+    <t>65.0396;88.2938;92.0497;42.8436;110.0609;11.8389;120.045;24.6445;122.0239;13.5245;148.0396;100</t>
+  </si>
+  <si>
+    <t>95.0678;248;95.0814;152;95.3338;56;96.2221;188;96.8713;40;97.0108;564;97.0393;948;97.2066;168;97.7391;156;98.005;168;98.0956;208;98.5653;128;98.8936;192;98.9778;192;99.0322;212;99.056;144;99.2978;164;99.6412;224;100.0228;180;100.6631;100;101.905;104;101.9532;172;103.0029;200;103.0575;208;103.9383;176;104.056;112;105.0684;596;106.029;164;106.0695;156;107.0829;196;107.5939;84;107.8563;40;108.0403;144;108.0821;176;108.3654;180;110.0271;212;110.0459;124;110.1002;188;110.8617;124;110.9817;188;111.0229;204;111.0536;164;112.0236;120;112.0407;164;113.0343;112;113.3293;156;113.8448;128;114.0041;164;114.0338;296;115.003;164;115.0307;184;115.0539;180;116.0169;132;117.0697;204;117.5505;60;117.6627;168;118.478;56;120.139;232;120.9563;116;121.0132;184;121.0657;212;121.4646;144;121.4997;120;122.0181;168;122.0994;320;122.6168;148;123.005;188;123.0266;1444;123.1008;140;124.0284;320;125.0348;124;125.0732;180;125.657;192;125.9428;212;125.998;152;126.0443;320;127.0172;160;127.0733;128;128.5426;100;129.0305;188;129.0463;196;131.03;128;131.9337;156;132.0831;220;133.0632;136;133.0862;184;134.0177;60;134.7168;208;135.5613;176;136.0764;152;137.0694;216;137.9983;280;138.0401;364;138.1832;44;138.9517;32;139.0174;180;139.0555;512;139.567;44;139.8588;180;140.0376;160;140.0544;168;141.0121;172;141.0594;208;142.0303;168;142.0672;204;142.7023;168;143.0307;152;149.042;472;149.1236;40;151.0768;392;151.0939;152;151.2334;80;151.2677;184;152.9172;60;153.1043;168;154.0687;132;155.0229;300;155.9744;176;156.0428;180;156.0804;196;158.0619;124;158.3022;56;163.0801;160;164.0543;192;165.104;180;166.0654;516;166.1398;32;167.0542;588;168.0573;384;169.0509;172;171.5631;68;174.2982;132;175.0769;208;175.1401;144;175.7253;76;176.412;156;177.1026;148;181.1087;144;183.0612;184;184.0789;520;185.077;432;186.0737;180;186.557;120;187.0439;116;187.0875;124;192.0535;220;193.0939;204;199.0049;112;199.0944;328;202.0856;152;203.1565;156;204.3128;76;205.4523;184;209.076;760;210.0567;108;211.2671;68;211.4812;48;221.0548;160;223.9703;196;226.4613;224;226.7939;136;226.8719;120;226.9678;156;227.0852;2136;228.0881;216;229.0716;116;229.0987;84;229.5965;164;229.8223;64;252.7022;80;400.8387;104;592.8976;48;791.9004;52;816.4515;136;825.3817;132;840.6501;124;862.9438;224;905.5893;204;940.0019;188;951.1835;144;1013.8486;140;1032.4828;208;1069.3162;128;1074.3335;96;1078.6499;164;1097.3796;128;1153.6066;20;1167.7;160;1169.217;204;1176.7152;164;1193.3916;264;1206.8367;228;1218.5638;176;1228.6658;56;1230.215;164;1231.0459;168;1234.7917;84;1239.0336;60;1242.7144;124;1254.8679;40;1280.0288;140;1282.9857;156;1288.1309;252;1288.9095;160;1290.0531;192;1311.8402;136;1314.8407;136;1318.4083;228;1332.1312;28;1332.2548;140;1340.52;180;1347.2325;144;1349.5859;20;1352.0437;192;1368.8104;180;1386.7994;212;1386.8735;264;1390.7452;168;1396.4738;188;1412.2411;184;1431.3405;244;1433.751;232;1445.5618;148;1461.1846;148;1471.3054;128;1475.1097;172;1478.4368;160;1485.0868;180</t>
+  </si>
+  <si>
+    <t>166.087;1.0524;200.0755;3.4553;209.093;1.3124;243.0813;100;244.0841;12.7623;245.0773;4.9008</t>
+  </si>
+  <si>
+    <t>122.0972;7.7485;156.0857;10.0819;165.1036;4.9341;166.0875;30.3349;167.0907;3.046;197.0929;5.7535;199.0913;3.9188;200.0753;60.5451;201.0785;5.7;202.0713;2.4225;209.0938;8.8885;243.0815;100;244.0846;12.5579;245.0773;4.9163</t>
+  </si>
+  <si>
+    <t>97.0408;0.10572;111.0454;0.10094;120.0821;0.25258;122.0976;0.50464;156.0855;1.1715;165.1037;1.2987;166.0875;7.8919;191.0829;0.21443;197.0935;0.73047;199.0914;3.4352;200.0751;19.2729;209.0933;3.4414;225.0706;0.14871;243.081;100</t>
+  </si>
+  <si>
+    <t>227.0846;59.5204;228.0875;5.7698;229.0813;2.1638;245.0953;100;246.0981;10.0148;247.092;4.1333</t>
+  </si>
+  <si>
+    <t>166.0685;1.6376;167.0525;2.8378;184.0789;2.6411;199.0898;2.9879;209.0741;3.1696;227.0847;100;228.0875;9.7786;229.081;3.7946;245.0952;4.1889</t>
+  </si>
+  <si>
+    <t>97.0398;13.866;98.0967;1.1973;100.0219;1.3585;101.0424;1.073;105.07;8.7313;107.0858;1.667;108.0809;2.3072;111.0264;2.2427;112.022;1.3355;113.0423;3.0025;115.057;2.9565;120.0809;1.1467;121.0651;2.4591;122.0966;3.1591;123.0266;22.7262;124.0291;1.2065;125.0421;4.1953;131.0277;1.5888;132.081;1.271;133.0651;2.5374;136.0758;1.0408;138.0011;1.7315;139.0579;21.5934;143.0276;4.3196;148.076;1.842;149.0422;5.3097;150.0916;3.463;151.0867;6.9215;153.1027;2.9933;154.0689;1.6578;155.0278;1.7822;156.0845;4.49;163.0866;2.1782;164.0535;1.5013;165.1024;2.7446;166.0687;23.8499;167.0527;21.5059;168.0563;2.2197;181.0974;1.7545;182.0637;4.9413;184.0792;21.8098;185.0756;5.8991;186.0757;1.4828;192.0478;5.9452;193.0975;1.4921;199.09;26.53;200.0931;2.6157;201.0866;1.2664;209.0745;13.2811;210.0586;1.598;227.085;100;228.0879;10.2878;229.0815;4.2229</t>
+  </si>
+  <si>
+    <t>79.0535;2.9424;81.0684;2.1251;82.0272;3.4123;85.0096;3.6984;91.0546;6.5999;93.0703;4.2705;94.065;2.9015;95.0852;3.8619;96.0805;2.2477;97.0395;60.5435;98.0964;2.3089;99.0262;4.7405;100.0217;6.5999;101.0421;3.5962;102.0005;2.452;103.0545;3.5962;105.07;66.4078;106.0668;5.3126;107.0858;4.8018;108.0811;11.0339;109.0651;3.6984;110.0962;2.5541;111.0264;18.5125;112.0216;11.2178;113.0421;9.2971;114.0372;2.5746;115.0553;8.3163;118.0653;3.2897;120.0809;7.499;121.065;5.7213;122.0966;11.2995;123.0265;100;124.0294;5.9256;125.042;17.9199;126.0013;4.1275;130.0666;2.9628;131.0281;2.0842;132.0807;6.9677;133.0888;12.076;134.0603;4.8835;136.0761;3.7188;137.0711;5.2513;138.001;12.7707;139.0578;53.7597;140.0549;5.5578;141.0539;2.5541;142.0324;3.5349;143.0273;6.5591;148.0761;5.4557;149.0419;13.3837;150.0915;5.19;151.0868;19.7998;152.0934;3.8619;153.1023;10.564;154.0686;5.9461;155.0277;4.7405;156.0844;9.9305;163.0866;6.2526;164.0529;4.3318;165.1025;7.2129;166.0684;33.8169;167.0526;19.3707;181.0972;2.0842;182.0634;6.273;184.079;21.9657;185.0748;10.8296;192.0479;7.0494;199.0898;20.5762;200.0922;2.1864;209.0742;7.2946;227.0848;25.3167;228.0875;2.6154</t>
+  </si>
+  <si>
+    <t>91.0544;18.0169;93.0703;8.0701;94.0652;8.508;97.0397;81.9831;99.0267;9.6028;100.0216;11.198;103.0543;11.3544;105.0701;78.1045;106.0667;11.5733;108.0809;14.4198;111.0265;33.0622;112.0218;17.9231;113.0424;9.5402;115.0548;7.8824;118.0653;7.8198;120.0807;9.6028;122.0965;8.1639;123.0264;100;124.03;7.6947;125.0295;16.6406;132.0808;10.6662;133.0888;10.5724;134.0188;7.9762;138.0008;18.2358;139.0576;19.3306;151.0867;7.9762</t>
+  </si>
+  <si>
+    <t>76.0216;0.54143;79.0542;0.44205;81.0699;0.49782;82.0289;0.28751;83.0493;0.16714;85.0107;0.49151;87.0266;0.12056;91.0543;0.25367;95.0853;0.25057;97.0107;1.4647;97.0396;7.1321;98.0965;0.44152;99.026;0.24369;100.0216;0.37787;101.042;0.33382;102.0006;0.28787;105.07;1.8739;107.0855;0.51583;108.0809;0.76525;109.0639;0.17576;111.0265;0.52299;112.0212;0.24372;113.0419;0.67315;115.058;0.75233;120.0811;0.2535;121.0647;0.88461;122.0966;0.55476;123.0263;5.89;124.0757;0.15046;125.0421;1.0801;126.0011;0.14161;131.0273;0.55302;132.081;0.18492;133.065;0.63558;133.0889;0.33232;137.0421;0.11166;138.0005;0.22727;138.037;0.40279;139.0577;4.4624;140.0523;0.14383;141.0117;0.1812;143.0274;1.1783;143.0523;0.14627;148.0756;0.13565;150.0915;1.0615;151.0865;1.1246;153.1026;0.42385;154.0682;0.22162;156.0484;0.23864;156.0843;0.95959;162.0919;0.10705;163.0858;0.29665;164.053;0.3832;165.1028;0.54267;166.0687;7.4004;167.0527;7.6382;172.9873;0.1271;173.0381;0.19128;173.0549;0.10127;173.1047;0.13711;173.1236;0.10846;175.0874;0.18982;181.0975;0.33899;182.0634;1.1329;183.058;0.14426;184.0792;7.601;185.0743;1.2238;192.0481;2.2297;193.0976;0.61182;199.0901;9.0948;209.0746;7.802;210.0585;0.78979;227.0851;100;245.0954;0.89593</t>
+  </si>
+  <si>
+    <t>105.055;0.001001;105.5469;0.002002;110.0692;0.001001;110.071;0.051051;110.0725;0.001001;110.0732;0.001001;111.0744;0.001001;113.7076;0.001001;113.9333;0.001001;113.9443;0.001001;113.9967;0.002002;113.9995;0.001001;114.0215;0.001001;114.039;0.004004;114.042;0.001001;114.0429;0.001001;114.0445;0.001001;114.0452;0.001001;114.0473;0.001001;114.048;0.001001;114.0484;0.001001;114.0498;0.001001;114.0503;0.001001;114.0521;0.001001;114.0526;0.001001;114.0535;0.001001;114.0544;0.004004;114.0551;0.001001;114.0567;0.006006;114.0583;0.013013;114.0602;1;114.0618;0.01001;114.0625;0.011011;114.0634;0.005005;114.0641;0.006006;114.0652;0.002002;114.0659;0.003003;114.0671;0.001001;114.0675;0.001001;114.068;0.001001;114.0687;0.001001;114.0698;0.001001;114.0705;0.001001;114.0728;0.001001;114.0758;0.001001;114.0781;0.001001;114.0788;0.001001;114.0816;0.004004;114.0846;0.001001;114.0988;0.001001;114.1212;0.001001;114.1239;0.002002;114.1762;0.001001;114.1875;0.001001;114.4144;0.001001;114.559;0.002002;114.5614;0.085085;114.5637;0.001001;114.5655;0.001001;115.0621;0.001001;115.0626;0.001001;137.132;0.001001;138.0658;0.001001;141.9582;0.001001;149.0226;0.001001;149.0418;0.005005;149.5435;0.001001;152.0817;0.044044;153.0849;0.001001;156.0425;0.001001;156.0672;0.001001;156.0705;0.001001;156.0734;0.002002;156.0764;0.17518;156.0786;0.001001;156.0797;0.002002;156.0815;0.001001;156.0826;0.001001;157.0733;0.001001;157.0796;0.008008;158.0026;0.014014;161.5329;0.001001;163.1323;0.001001;165.5368;0.001001;171.1487;0.011011;174.1272;0.003003;179.0632;0.001001;180.0727;0.001001;180.0763;0.093093;180.0795;0.001001;180.0809;0.001001;181.0796;0.003003;182.0918;0.012012;182.9843;0.002002;187.1256;0.001001;198.0784;0.001001;198.0826;0.002002;198.0869;0.16717;198.0895;0.002002;198.0905;0.001001;198.0916;0.001001;198.0942;0.001001;198.0958;0.001001;199.0286;0.001001;199.0896;0.008008;199.1793;0.001001;210.0868;0.01001;223.0632;0.001001;226.9345;0.001001;227.0533;0.001001;227.0915;0.001001;227.0966;0.002002;227.1031;0.003003;227.1076;0.005005;227.1128;0.54555;227.1173;0.004004;227.1193;0.005005;227.1218;0.002002;227.1244;0.002002;227.127;0.001001;227.129;0.001001;227.1303;0.001001;227.1729;0.002002;227.2214;0.001001;227.292;0.001001;228.1104;0.004004;228.1162;0.05005;229.1171;0.001001;229.1191;0.001001;254.0717;0.001001;282.2212;0.001001;297.0756;0.001001;391.2829;0.018018;392.2848;0.002002;453.2191;0.013013;453.2264;0.001001;454.2213;0.001001</t>
+  </si>
+  <si>
+    <t>72.0241;0.13013;73.0025;0.011011;90.0121;0.026026;91.0147;0.013013;96.5685;0.003003;99.5668;0.002002;105.3787;0.15115;109.9533;0.14515;138.074;0.034034;152.007;0.21221;153.3394;0.002002;156.056;1;157.1546;0.01001;180.0829;0.51852;181.08;0.003003;182.1525;0.071071;192.0567;0.015015;198.0437;0.62262;199.0186;0.006006;210.1292;0.033033</t>
+  </si>
+  <si>
+    <t>82.924;0.003003;95.0399;0.033033;109.9994;1;110.8359;0.001001;112.1104;0.006006;138.0371;0.008008;139.0078;0.001001;147.1679;0.001001;156.067;0.001001</t>
+  </si>
+  <si>
+    <t>83.0969;0.001001;90.0541;0.001001;93.172;0.001001;109.9999;0.15215;122.1279;0.001001;138.1581;0.055055;152.2907;0.001001;154.1694;0.005005;156.2075;0.1011;164.2027;0.002002;180.0996;0.10911;181.1359;0.026026;182.0613;0.004004;192.1074;0.026026;198.171;0.01001;209.352;0.32933;210.1457;1</t>
+  </si>
+  <si>
+    <t>100.1118;0.001001;102.0337;0.001001;105.055;0.001001;105.5471;0.001001;110.0675;0.001001;110.0712;0.049049;110.0723;0.001001;111.0746;0.001001;113.7078;0.001001;113.939;0.001001;113.9969;0.002002;114.0202;0.001001;114.0358;0.001001;114.0392;0.006006;114.0459;0.001001;114.0468;0.001001;114.0487;0.001001;114.0498;0.001001;114.051;0.001001;114.0514;0.001001;114.0524;0.002002;114.0544;0.003003;114.0556;0.002002;114.0567;0.005005;114.0574;0.002002;114.0583;0.01001;114.0604;1;114.0623;0.011011;114.0641;0.005005;114.0652;0.003003;114.0664;0.003003;114.0671;0.001001;114.0682;0.002002;114.0689;0.001001;114.0703;0.001001;114.071;0.001001;114.0724;0.001001;114.0738;0.001001;114.0744;0.001001;114.0754;0.001001;114.0795;0.001001;114.0816;0.006006;114.1009;0.001001;114.1242;0.002002;114.182;0.001001;114.4147;0.001001;114.5579;0.001001;114.5593;0.002002;114.5618;0.091091;114.5637;0.001001;114.5829;0.001001;115.0619;0.001001;115.063;0.001001;129.1017;0.001001;129.1023;0.001001;130.0862;0.048048;130.0876;0.001001;130.0884;0.001001;131.0894;0.001001;137.132;0.001001;138.0661;0.001001;141.9585;0.002002;147.0194;0.001001;147.0814;0.003003;147.0929;0.001001;147.1009;0.001001;147.1036;0.002002;147.1047;0.001001;147.1053;0.001001;147.107;0.003003;147.108;0.001001;147.1094;0.006006;147.1124;0.58158;147.1154;0.006006;147.1181;0.003003;147.1198;0.001001;147.1212;0.002002;147.1225;0.001001;147.1239;0.001001;147.1249;0.001001;147.1279;0.001001;147.132;0.001001;147.1434;0.003003;147.1721;0.001001;147.2058;0.001001;147.2905;0.001001;147.6315;0.001001;148.1097;0.001001;148.1158;0.034034;149.0229;0.002002;149.0418;0.001001;149.1164;0.001001;152.0817;0.034034;153.0853;0.001001;155.1429;0.001001;156.0425;0.001001;156.0705;0.001001;156.0731;0.002002;156.0764;0.14715;156.0797;0.001001;156.0823;0.001001;156.1103;0.001001;157.0733;0.001001;157.0796;0.006006;158.0026;0.004004;158.0964;0.001001;161.5329;0.001001;163.1323;0.001001;163.5183;0.001001;169.0942;0.004004;171.1373;0.001001;171.1491;0.015015;173.0777;0.001001;174.1276;0.007007;179.0632;0.001001;180.0727;0.001001;180.0768;0.079079;180.0804;0.001001;181.0796;0.003003;181.1082;0.001001;182.0918;0.007007;182.9848;0.004004;185.1141;0.004004;187.1261;0.002002;193.1307;0.003003;198.0821;0.001001;198.0874;0.13013;198.0916;0.001001;198.1353;0.001001;199.0901;0.006006;199.1798;0.001001;209.1027;0.001001;210.0805;0.001001;210.0868;0.008008;217.1041;0.001001;223.0626;0.001001;223.0651;0.001001;226.1237;0.001001;226.7725;0.001001;226.9351;0.001001;227.054;0.003003;227.0753;0.001001;227.0908;0.001001;227.0934;0.001001;227.096;0.002002;227.0986;0.001001;227.0999;0.001001;227.1031;0.003003;227.105;0.001001;227.1076;0.006006;227.1134;0.72673;227.1186;0.006006;227.1238;0.003003;227.127;0.001001;227.1296;0.002002;227.1322;0.001001;227.1354;0.001001;227.1374;0.001001;227.1503;0.001001;227.1729;0.003003;227.2926;0.001001;227.4552;0.001001;228.111;0.005005;228.1169;0.063063;229.1171;0.002002;249.0951;0.013013;250.0976;0.001001;255.156;0.001001;271.0764;0.001001;293.217;0.003003;299.1816;0.002002;301.1146;0.004004;301.1185;0.001001;373.2177;0.007007;373.2231;0.001001;374.2207;0.001001;391.2829;0.013013;392.2863;0.002002;413.2651;0.007007;414.2667;0.001001;429.238;0.001001;453.2191;0.022022;454.2213;0.002002;475.1991;0.002002;519.1624;0.001001;537.3873;0.002002;803.54;0.001001;1343.9056;0.001001</t>
+  </si>
+  <si>
+    <t>71.9939;0.13213;73.0595;0.01001;90.1059;0.024024;90.9925;0.015015;105.3428;0.17117;106.2214;0.008008;110.0034;0.13814;134.296;0.006006;138.0382;0.019019;152.0647;0.19119;154.072;0.002002;156.1239;1;157.1071;0.031031;180.074;0.52152;181.1599;0.033033;182.0653;0.057057;198.0679;0.73574;199.1559;0.027027;210.25;0.011011</t>
+  </si>
+  <si>
+    <t>84.0024;0.038038;101.1211;0.002002;129.1466;0.084084;130.0932;1</t>
+  </si>
+  <si>
+    <t>83.05;0.001001;90.0507;0.001001;93.0486;0.001001;110.0011;0.13714;137.9816;0.047047;152.182;0.002002;154.2012;0.004004;156.0725;0.09009;164.1878;0.002002;180.0774;0.1001;181.1244;0.02002;182.1903;0.004004;192.1177;0.022022;198.2188;0.01001;209.1038;0.21822;210.0672;1</t>
+  </si>
+  <si>
+    <t>108.0568;0.003003;109.0409;0.001001;110.012;0.001001;110.0523;0.002002;110.06;0.001001;110.0626;0.001001;110.065;0.001001;110.0659;0.001001;110.0667;0.002002;110.0689;0.004004;110.0704;0.014014;110.0724;0.35636;110.0742;0.015015;110.0752;0.003003;110.0761;0.004004;110.0768;0.001001;110.0779;0.002002;110.08;0.001001;110.0822;0.001001;110.0846;0.001001;110.0925;0.002002;110.1329;0.001001;111.0692;0.002002;111.0739;0.001001;111.0757;0.014014;112.9856;0.013013;127.051;0.007007;137.0356;0.006006;139.0069;0.001001;145.0617;0.001001;152.0828;0.003003;154.0531;0.001001;154.0571;0.001001;154.0589;0.004004;154.0621;0.11712;154.065;0.004004;154.0668;0.001001;154.0683;0.001001;154.0954;0.001001;155.059;0.001001;155.0652;0.006006;161.0829;0.001001;163.0985;0.007007;163.9912;0.001001;164.0825;0.008008;179.0937;0.001001;181.1056;0.002002;181.1093;0.06006;181.1135;0.002002;182.1123;0.003003;187.9941;0.002002;207.0882;0.003003;215.9892;0.002002;224.804;0.001001;224.9212;0.002002;224.9288;0.001001;225.0015;0.001001;225.0232;0.001001;225.0276;0.001001;225.0391;0.005005;225.0436;0.001001;225.0461;0.001001;225.0595;0.001001;225.0615;0.001001;225.0697;0.001001;225.0768;0.002002;225.0793;0.002002;225.0819;0.004004;225.0844;0.002002;225.0876;0.008008;225.0927;0.029029;225.0978;1;225.1036;0.029029;225.1068;0.006006;225.1087;0.007007;225.1144;0.005005;225.117;0.002002;225.1202;0.001001;225.1246;0.001001;225.1265;0.001001;225.1323;0.001001;225.1342;0.001001;225.1361;0.001001;225.1438;0.001001;225.1514;0.001001;225.1565;0.004004;225.1597;0.001001;225.1623;0.001001;225.1687;0.001001;225.175;0.001001;225.1955;0.001001;225.2747;0.002002;225.3923;0.001001;226.0901;0.001001;226.0926;0.001001;226.0959;0.011011;226.1016;0.085085;226.1074;0.002002;227.0986;0.001001;227.1025;0.004004;228.1061;0.001001;230.9972;0.001001;232.0201;0.001001;233.0121;0.003003;233.9991;0.001001;234.02;0.003003;235.0284;0.002002;249.0563;0.001001;257.9992;0.001001;261.0752;0.001001;267.0604;0.001001;267.0678;0.03003;267.0744;0.001001;268.002;0.001001;268.0708;0.002002;269.0628;0.004004;278.0103;0.001001;279.0184;0.002002;280.0258;0.001001;281.0334;0.001001;285.0302;0.001001;285.0775;0.001001;286.0302;0.001001;287.0262;0.014014;288.0293;0.001001;288.094;0.002002;289.0219;0.001001;292.026;0.001001;293.0858;0.001001;295.0618;0.003003;297.0279;0.001001;305.0367;0.002002;309.0507;0.001001;311.0072;0.001001;313.0723;0.001001;314.9942;0.001001;315.0681;0.001001;316.9915;0.001001;320.021;0.001001;323.0656;0.006006;323.0755;0.001001;325.0229;0.004004;325.1835;0.001001;333.0314;0.003003;339.0516;0.004004;339.0917;0.005005;340.0552;0.001001;340.0943;0.001001;341.0681;0.002002;345.0452;0.001001;345.0476;0.002002;347.0238;0.001001;359.0463;0.001001;365.1132;0.001001;367.989;0.001001;370.9894;0.001001;371.9823;0.002002;376.985;0.001001;391.0505;0.001001;451.0382;0.001001;451.1595;0.001001;451.1758;0.001001;451.1902;0.004004;451.2047;0.24625;451.221;0.005005;451.2301;0.001001;451.2355;0.001001;452.1914;0.001001;452.2078;0.043043;452.2241;0.001001;453.2032;0.001001;453.2123;0.003003;454.2111;0.001001;460.1262;0.006006;461.1292;0.001001;473.1706;0.001001;473.1861;0.067067;473.2037;0.001001;474.1912;0.011011;475.1623;0.023023;475.1936;0.001001;476.0991;0.001001;476.1658;0.004004;477.1686;0.001001;489.1522;0.002002;489.1604;0.002002;493.1728;0.001001;495.1694;0.004004;496.1722;0.001001;500.1212;0.001001;503.129;0.001001;504.1176;0.012012;505.1242;0.029029;506.1273;0.005005;507.1248;0.002002;509.12;0.001001;509.3067;0.001001;511.1379;0.002002;512.1349;0.002002;513.1129;0.001001;513.1217;0.001001;513.1327;0.028028;514.1356;0.005005;515.1281;0.002002;519.3128;0.001001;521.169;0.009009;522.1708;0.001001;527.1064;0.001001;535.1587;0.003003;535.3061;0.004004;535.3225;0.001001;536.1612;0.001001;536.3113;0.001001;537.3029;0.002002;538.3044;0.001001;541.102;0.001001;547.2149;0.001001;549.1743;0.001001;550.1213;0.001001;551.1295;0.001001;555.2642;0.001001;561.3202;0.001001;563.3003;0.009009;564.307;0.002002;565.1589;0.003003;565.1945;0.001001;571.151;0.002002;572.1555;0.001001;651.3909;0.001001;671.3991;0.001001;677.3114;0.007007;678.3149;0.002002;689.3589;0.001001;691.4049;0.001001;697.3961;0.001001;699.2928;0.005005;700.2966;0.001001;701.2709;0.025025;702.2719;0.006006;703.2786;0.001001;713.2892;0.001001;715.2584;0.005005;715.4066;0.001001;716.2606;0.001001;717.4027;0.001001;721.2774;0.002002;723.2541;0.001001;729.2368;0.001001;730.2237;0.008008;731.2314;0.014014;732.2336;0.004004;737.2417;0.001001;739.2388;0.005005;740.2424;0.001001;767.3853;0.001001;775.2773;0.002002;776.2816;0.001001;791.267;0.001001;797.2596;0.001001;877.4989;0.001001;893.6296;0.001001;897.5032;0.001001;903.4198;0.009009;904.4211;0.004004;905.424;0.001001;905.9801;0.001001;917.6529;0.001001;918.6516;0.001001;919.6308;0.002002;920.6327;0.001001;925.4009;0.005005;926.407;0.002002;927.3773;0.002002;928.3812;0.001001;939.3967;0.001001;949.3646;0.001001;957.3396;0.004004;958.3421;0.001001;965.3474;0.001001;979.3182;0.001001;987.3284;0.001001;1001.3855;0.001001;1005.9753;0.004004;1006.9767;0.001001;1073.7359;0.001001;1074.7337;0.001001;1099.731;0.001001;1100.7308;0.001001;1101.7388;0.001001;1103.6066;0.001001;1105.9654;0.005005;1106.9737;0.001001;1129.5236;0.01001;1130.5283;0.005005;1131.5344;0.002002;1132.5347;0.001001;1151.5061;0.001001;1152.5182;0.001001;1153.4871;0.001001;1165.9853;0.005005;1166.9939;0.001001;1167.4761;0.001001;1183.4422;0.002002;1191.4512;0.001001;1205.9646;0.002002;1233.97;0.001001;1243.0777;0.001001;1265.9781;0.008008;1266.9829;0.002002;1280.8301;0.001001;1305.9539;0.001001;1333.9663;0.002002;1334.9795;0.001001;1355.628;0.003003;1356.1279;0.001001;1356.6376;0.002002;1357.6483;0.001001;1365.975;0.005005;1366.9675;0.001001;1382.957;0.001001;1409.5499;0.001001;1433.958;0.002002;1465.9691;0.003003;1466.9664;0.001001;1469.6771;0.001001</t>
+  </si>
+  <si>
+    <t>86.015;0.001001;88.0252;0.032032;110.1193;0.055055;134.2151;0.002002;136.0904;0.004004;137.1241;0.004004;139.1084;0.002002;145.9724;0.004004;152.0775;0.001001;154.0445;1;161.2748;0.002002;163.1189;0.30731;164.1032;0.005005;181.1301;0.044044;195.9865;0.002002;206.9951;0.055055;208.1472;0.011011</t>
+  </si>
+  <si>
+    <t>154.0516;0.022022;163.1573;0.013013;225.134;1;360.971;0.002002;376.3322;0.003003</t>
+  </si>
+  <si>
+    <t>102.949;0.001001;102.9571;0.001001;106.0412;0.001001;108.057;0.003003;110.0124;0.001001;110.0526;0.002002;110.0648;0.001001;110.0663;0.001001;110.0672;0.001001;110.0689;0.004004;110.0709;0.011011;110.0726;0.27528;110.0744;0.01001;110.0761;0.005005;110.0772;0.001001;110.0787;0.001001;110.0927;0.002002;111.0697;0.001001;111.0759;0.011011;112.965;0.001001;112.982;0.001001;112.9841;0.003003;112.9859;0.067067;112.9877;0.002002;112.9895;0.001001;113.9893;0.001001;114.9521;0.001001;127.0513;0.01001;127.0529;0.001001;129.9756;0.001001;137.0356;0.006006;142.9465;0.001001;145.0928;0.001001;145.0957;0.001001;145.0984;0.023023;145.1013;0.001001;146.1014;0.001001;146.9385;0.001001;152.0828;0.002002;154.0563;0.001001;154.0592;0.003003;154.0621;0.10911;154.0654;0.003003;154.0683;0.001001;155.0656;0.006006;157.0118;0.004004;163.0989;0.007007;164.0829;0.007007;174.065;0.007007;176.0437;0.001001;180.9731;0.014014;180.9749;0.001001;181.1015;0.001001;181.1056;0.001001;181.1093;0.049049;181.113;0.001001;182.1127;0.004004;184.3337;0.001001;186.0645;0.001001;186.9292;0.001001;190.928;0.001001;198.936;0.002002;206.9728;0.001001;207.0887;0.003003;208.0917;0.001001;210.9995;0.001001;213.0756;0.001001;213.0809;0.001001;213.0856;0.047047;213.0897;0.001001;214.0887;0.002002;218.0543;0.008008;224.9225;0.002002;224.9945;0.001001;224.9983;0.001001;225.0053;0.001001;225.0219;0.001001;225.0398;0.005005;225.0436;0.001001;225.05;0.001001;225.0519;0.001001;225.0627;0.001001;225.0761;0.002002;225.08;0.003003;225.0831;0.003003;225.0882;0.012012;225.0934;0.028028;225.0985;1;225.1042;0.026026;225.1093;0.011011;225.1138;0.002002;225.1163;0.003003;225.1182;0.002002;225.1214;0.002002;225.1253;0.001001;225.1342;0.001001;225.1367;0.001001;225.1393;0.001001;225.147;0.001001;225.1572;0.004004;225.1667;0.001001;225.1706;0.001001;225.175;0.001001;225.2019;0.001001;225.2753;0.002002;225.3929;0.001001;226.0914;0.001001;226.0959;0.011011;226.1023;0.082082;226.1074;0.002002;226.1126;0.001001;227.1031;0.005005;228.9487;0.001001;230.0542;0.006006;233.0128;0.001001;234.0207;0.001001;235.0284;0.001001;238.9313;0.001001;247.0685;0.001001;247.0751;0.003003;247.081;0.091091;247.0846;0.002002;247.0876;0.002002;247.0927;0.001001;248.0841;0.006006;248.9546;0.001001;248.9598;0.036036;248.965;0.001001;249.9632;0.002002;254.9165;0.001001;257.1121;0.001001;258.0008;0.001001;261.0673;0.001001;264.9343;0.001001;267.0678;0.002002;271.0415;0.001001;281.0343;0.001001;281.0725;0.013013;282.0759;0.001001;283.0576;0.013013;284.0608;0.001001;285.0311;0.001001;285.0548;0.003003;287.0262;0.004004;291.0282;0.002002;292.9863;0.001001;292.9995;0.001001;293.0536;0.001001;293.0592;0.001001;293.063;0.001001;293.0706;0.004004;293.0791;0.009009;293.0867;0.36637;293.0953;0.008008;293.0991;0.001001;293.1019;0.004004;293.1066;0.001001;293.1133;0.001001;293.1161;0.001001;293.174;0.001001;294.0837;0.004004;294.0894;0.033033;294.0942;0.001001;294.097;0.001001;295.0618;0.001001;295.0905;0.001001;295.0934;0.001001;296.937;0.001001;297.0289;0.001001;299.0362;0.001001;299.1007;0.003003;305.0397;0.001001;306.9196;0.001001;307.0364;0.001001;307.073;0.001001;309.0518;0.002002;309.061;0.001001;310.0767;0.006006;313.1853;0.003003;314.1888;0.001001;315.0512;0.001001;315.0597;0.004004;315.0681;0.12913;315.0777;0.003003;315.0861;0.001001;315.1622;0.001001;316.0658;0.001001;316.0722;0.01001;316.9392;0.001001;316.9477;0.032032;316.9552;0.001001;317.9512;0.001001;320.0221;0.001001;324.0156;0.001001;325.024;0.004004;326.0271;0.001001;331.0367;0.001001;331.0424;0.001001;332.9212;0.001001;333.0314;0.005005;334.9109;0.001001;337.1126;0.01001;338.1159;0.001001;341.0681;0.001001;345.0488;0.003003;347.0067;0.001001;349.0503;0.001001;349.0602;0.019019;350.064;0.002002;351.0449;0.001001;355.0566;0.001001;359.0951;0.001001;360.9744;0.001001;361.0638;0.002002;361.0741;0.074074;361.0858;0.002002;362.077;0.008008;367.0306;0.001001;367.0891;0.002002;373.0268;0.001001;375.0248;0.001001;377.0472;0.001001;381.1724;0.002002;383.0323;0.001001;383.0365;0.001001;383.045;0.002002;383.0564;0.086086;383.0677;0.002002;383.079;0.001001;384.0597;0.01001;384.9343;0.014014;385.0599;0.001001;385.938;0.001001;387.0951;0.001001;389.0116;0.001001;393.0112;0.001001;393.1746;0.001001;393.1864;0.035035;393.1967;0.001001;394.1899;0.004004;395.1632;0.001001;399.0292;0.003003;400.0447;0.001001;400.9093;0.001001;402.8988;0.001001;405.0387;0.001001;405.1004;0.002002;414.9935;0.002002;415.1693;0.006006;416.1716;0.001001;417.0472;0.017017;419.0334;0.002002;425.1244;0.002002;426.0217;0.001001;427.082;0.001001;429.0481;0.001001;429.0615;0.06006;429.0766;0.001001;430.064;0.006006;431.0345;0.001001;431.065;0.001001;433.0212;0.001001;433.1319;0.001001;435.0165;0.001001;441.0158;0.001001;441.1698;0.001001;445.0361;0.003003;446.0399;0.001001;449.1601;0.004004;451.0291;0.001001;451.0436;0.047047;451.0563;0.001001;451.2065;0.003003;452.0479;0.004004;452.9226;0.007007;453.0483;0.001001;453.9259;0.001001;461.1741;0.01001;462.1767;0.001001;467.0183;0.003003;473.0092;0.001001;473.0228;0.001001;473.0889;0.001001;473.1181;0.001001;473.1317;0.001001;473.1395;0.001001;473.155;0.004004;473.1725;0.009009;473.1881;0.46446;473.2056;0.008008;473.2134;0.001001;473.2192;0.004004;473.2289;0.001001;473.2426;0.001001;473.2484;0.001001;473.2562;0.001001;473.2601;0.001001;473.3671;0.002002;473.7272;0.001001;474.158;0.001001;474.1756;0.002002;474.1912;0.088088;474.2088;0.002002;474.2224;0.001001;475.1642;0.001001;475.1936;0.006006;482.9813;0.001001;483.1558;0.009009;484.1586;0.001001;485.0353;0.01001;486.0399;0.001001;487.0192;0.001001;487.0416;0.001001;489.1625;0.005005;490.1656;0.001001;493.1127;0.001001;495.0694;0.001001;495.1527;0.001001;495.1694;0.032032;495.1839;0.001001;496.1722;0.005005;497.0315;0.001001;497.0483;0.042042;497.065;0.001001;498.0526;0.006006;499.0537;0.001001;501.0099;0.001001;503.0053;0.001001;505.1242;0.001001;511.1445;0.001001;513.0229;0.004004;513.1349;0.001001;517.1508;0.044044;517.1663;0.001001;518.1565;0.006006;519.0133;0.001001;519.0312;0.026026;519.1585;0.001001;520.0335;0.002002;520.9106;0.004004;525.0456;0.001001;527.1087;0.002002;529.0621;0.001001;529.161;0.019019;530.1651;0.002002;531.1467;0.003003;532.1495;0.001001;533.1249;0.002002;533.1435;0.001001;535.0044;0.003003;535.3061;0.001001;536.882;0.001001;541.0758;0.001001;541.1162;0.001001;541.1352;0.001001;541.1567;0.001001;541.1757;0.097097;541.1971;0.002002;541.2137;0.001001;542.1784;0.018018;543.1816;0.001001;545.1337;0.001001;547.1907;0.003003;549.0916;0.001001;550.9682;0.001001;551.1441;0.008008;552.1478;0.002002;553.0239;0.01001;553.1296;0.001001;554.0253;0.001001;555.0072;0.001001;557.1502;0.003003;558.1653;0.001001;561.0992;0.001001;561.275;0.001001;563.0579;0.001001;563.1564;0.02002;563.3029;0.001001;564.1601;0.003003;565.0168;0.001001;565.0371;0.033033;566.0408;0.004004;567.042;0.001001;568.9961;0.001001;569.1064;0.001001;575.112;0.001001;579.1301;0.001001;581.0095;0.004004;583.0096;0.001001;583.257;0.001001;585.1405;0.011011;585.202;0.001001;586.1446;0.001001;587.0196;0.012012;587.1217;0.001001;587.1405;0.001001;588.0231;0.002002;588.897;0.003003;593.1371;0.001001;597.1501;0.021021;598.1549;0.003003;599.1345;0.002002;602.9933;0.002002;603.1024;0.001001;609.0645;0.001001;609.1412;0.001001;609.1639;0.071071;609.1838;0.001001;609.1895;0.001001;610.1679;0.012012;611.1715;0.001001;613.123;0.002002;614.1252;0.001001;615.1184;0.001001;615.1761;0.002002;617.2482;0.001001;619.1299;0.004004;620.1353;0.001001;621.0115;0.006006;622.0126;0.001001;625.137;0.004004;629.2619;0.002002;631.124;0.001001;631.145;0.014014;632.1497;0.002002;633.0245;0.019019;634.0277;0.003003;636.9848;0.001001;641.2769;0.002002;647.1183;0.001001;648.124;0.001001;648.9978;0.003003;651.2433;0.001001;653.1029;0.001001;653.125;0.006006;653.1881;0.001001;654.129;0.001001;655.0054;0.006006;655.1067;0.001001;656.0105;0.001001;656.8844;0.001001;663.2569;0.001001;664.9642;0.001001;665.1359;0.014014;666.1417;0.003003;667.1205;0.001001;667.1401;0.001001;669.0977;0.001001;669.1206;0.001001;677.1249;0.001001;677.1515;0.045045;677.1748;0.001001;677.1815;0.001001;678.1547;0.008008;679.1568;0.001001;681.1105;0.002002;683.1064;0.001001;685.2398;0.001001;687.1007;0.001001;687.1177;0.004004;689;0.005005;690.9826;0.001001;693.1255;0.004004;697.0761;0.001001;697.25;0.002002;698.2528;0.001001;699.1321;0.006006;699.2963;0.003003;700.1355;0.002002;700.3001;0.001001;701.0114;0.01001;702.0189;0.002002;703.0215;0.001001;704.973;0.001001;705.1499;0.001001;709.2645;0.008008;710.2684;0.002002;715.103;0.001001;716.9854;0.003003;719.2141;0.001001;719.2323;0.001001;721.1127;0.005005;721.1749;0.001001;721.2481;0.001001;721.2774;0.037037;722.1199;0.001001;722.2812;0.01001;722.9932;0.002002;723.2835;0.001001;723.9933;0.001001;724.8737;0.001001;725.2352;0.001001;731.067;0.001001;731.2463;0.002002;733.1254;0.015015;734.1277;0.003003;735.1133;0.001001;735.1284;0.001001;737.0829;0.001001;737.2493;0.002002;743.2575;0.004004;744.2616;0.001001;745.0371;0.001001;745.137;0.025025;746.141;0.006006;747.147;0.001001;749.0993;0.002002;750.0997;0.001001;753.2261;0.002002;754.227;0.001001;755.1083;0.002002;756.9856;0.002002;761.1144;0.003003;762.1151;0.001001;765.2371;0.006006;766.2419;0.001001;767.1202;0.003003;768.1288;0.001001;768.9983;0.006006;770.0025;0.001001;772.9619;0.001001;777.1486;0.001001;777.2509;0.013013;778.2549;0.004004;779.2362;0.001001;779.2526;0.001001;781.2291;0.001001;783.0971;0.001001;784.976;0.002002;787.2246;0.002002;788.2271;0.001001;789.1016;0.003003;789.2273;0.001001;789.265;0.024024;790.2672;0.006006;790.9812;0.001001;791.2712;0.002002;792.8632;0.001001;793.2219;0.001001;795.2814;0.001001;799.0574;0.001001;799.2324;0.002002;800.2366;0.001001;801.1098;0.009009;802.1131;0.002002;803.1055;0.001001;805.0742;0.001001;805.2382;0.002002;806.2407;0.001001;811.2464;0.004004;812.2514;0.001001;813.1268;0.013013;814.1309;0.004004;815.1369;0.001001;817.0882;0.001001;818.0908;0.001001;821.212;0.001001;823.0915;0.001001;824.9774;0.001001;825.9766;0.001001;829.098;0.002002;830.1092;0.001001;833.2268;0.005005;834.2319;0.002002;835.1066;0.001001;835.2115;0.001001;836.1106;0.001001;836.9883;0.003003;837.9911;0.001001;845.2378;0.01001;846.2462;0.001001;847.2424;0.001001;848.231;0.001001;851.0806;0.001001;855.2095;0.001001;857.0884;0.003003;857.2544;0.012012;858.2558;0.003003;859.259;0.001001;861.2134;0.001001;862.2123;0.001001;865.3394;0.001001;867.2181;0.001001;869.098;0.005005;870.1058;0.001001;873.2273;0.001001;877.3467;0.001001;879.2351;0.001001;881.1147;0.008008;882.1137;0.001001;885.0762;0.001001;886.077;0.001001;889.1997;0.001001;889.365;0.002002;891.1667;0.001001;892.9587;0.001001;897.0867;0.002002;901.2128;0.003003;903.0967;0.001001;904.9763;0.001001;905.9801;0.001001;913.2258;0.007007;914.2277;0.003003;915.2365;0.001001;917.1856;0.001001;920.9494;0.001001;923.1924;0.001001;925.0713;0.001001;925.2361;0.008008;925.4009;0.001001;926.2418;0.003003;926.4016;0.001001;927.0572;0.001001;927.2439;0.001001;929.2048;0.001001;930.2116;0.001001;933.3229;0.001001;935.2112;0.001001;937.089;0.003003;938.0925;0.001001;941.0471;0.001001;941.2107;0.001001;945.3376;0.002002;946.3434;0.001001;947.224;0.001001;947.3837;0.002002;948.3872;0.001001;949.0994;0.004004;950.1056;0.001001;953.0671;0.001001;957.1941;0.001001;957.3507;0.003003;958.3533;0.001001;959.0655;0.001001;965.0754;0.001001;969.2008;0.002002;969.3662;0.004004;970.2049;0.001001;970.3648;0.002002;981.2143;0.005005;982.2138;0.002002;985.1749;0.001001;991.3497;0.001001;993.2277;0.006006;994.2279;0.002002;997.184;0.001001;1002.3202;0.001001;1005.0777;0.002002;1005.9753;0.002002;1009.202;0.001001;1013.3274;0.003003;1014.3276;0.001001;1015.2132;0.001001;1017.0859;0.002002;1018.0916;0.001001;1019.0989;0.001001;1021.0501;0.001001;1025.1741;0.001001;1025.3415;0.004004;1026.3472;0.001001;1037.1918;0.001001;1037.3559;0.002002;1038.3603;0.001001;1049.1973;0.003003;1050.2061;0.001001;1053.1637;0.001001;1059.338;0.001001;1061.2166;0.003003;1062.2231;0.001001;1065.1791;0.001001;1069.296;0.001001;1071.1813;0.001001;1077.1809;0.001001;1081.3139;0.002002;1085.0789;0.001001;1093.3305;0.003003;1094.3353;0.001001;1095.1428;0.001001;1105.1737;0.001001;1105.3403;0.002002;1105.9654;0.003003;1106.3408;0.001001;1109.3015;0.001001;1117.1892;0.002002;1125.4323;0.001001;1129.2009;0.001001;1130.2052;0.001001;1131.2109;0.001001;1133.1614;0.001001;1145.1687;0.001001;1149.3019;0.002002;1161.3131;0.003003;1162.3232;0.001001;1165.271;0.001001;1165.9928;0.002002;1166.9864;0.001001;1173.3314;0.001001;1174.3419;0.001001;1181.4219;0.001001;1185.1824;0.001001;1193.4272;0.001001;1196.2988;0.001001;1205.9646;0.001001;1217.279;0.001001;1217.4556;0.001001;1218.4594;0.001001;1229.2989;0.001001;1230.3092;0.001001;1241.3158;0.001001;1261.412;0.001001;1265.9866;0.006006;1266.9829;0.001001;1273.2686;0.001001;1273.4231;0.001001;1274.4368;0.001001;1297.2859;0.001001;1305.945;0.001001;1330.402;0.001001;1365.9845;0.005005;1366.9866;0.002002;1465.9797;0.002002;1466.9876;0.001001</t>
+  </si>
+  <si>
+    <t>88.0396;0.034034;93.1037;0.001001;110.0619;0.057057;127.1344;0.001001;134.0744;0.002002;136.0816;0.003003;137.0899;0.006006;139.1754;0.001001;146.0311;0.004004;152.2021;0.002002;153.9993;1;157.0176;0.001001;161.1019;0.004004;163.0066;0.3033;164.0456;0.004004;181.0633;0.049049;207.1279;0.053053;208.1835;0.01001</t>
+  </si>
+  <si>
+    <t>156.9774;0.001001;225.1074;1;247.0857;0.008008;264.0237;0.002002</t>
+  </si>
+  <si>
+    <t>136.0929;0.002002;144.0233;0.002002;146.0676;0.003003;154.1603;0.10611;163.1992;0.024024;164.2163;0.001001;181.0461;0.002002;207.1553;0.001001;225.0448;1;247.02;0.013013;405.1563;0.013013;426.8199;0.002002;455.3959;0.001001</t>
+  </si>
+  <si>
+    <t>110.0739;0.25425;156.0802;0.43544;210.0928;0.095095;227.1144;1</t>
+  </si>
+  <si>
+    <t>83.0611;0.12813;93.0459;0.10711;95.0616;0.11011;110.0721;1;122.0726;0.13113;156.0779;0.32132;164.0833;0.10511;181.1098;0.077077;210.0882;0.20721;227.1144;0.14915</t>
+  </si>
+  <si>
+    <t>81.0466;0.14414;93.0458;0.11111;110.0725;1;154.0623;0.79279;163.1012;0.11011;225.0196;0.17718;225.0988;0.72272</t>
+  </si>
+  <si>
+    <t>86.015;0.067747;88.0252;3.2047;110.1193;5.5046;134.2151;0.18451;136.0904;0.35318;137.1241;0.40739;139.1084;0.15996;145.9724;0.39429;152.0775;0.12857;154.0445;100;161.2748;0.21983;163.1189;30.6954;164.1032;0.51443;181.1301;4.4457;195.9865;0.15888;206.9951;5.5244;208.1472;1.1311</t>
+  </si>
+  <si>
+    <t>154.0516;2.189;163.1573;1.2863;225.134;100;360.971;0.20075;376.3322;0.34933</t>
+  </si>
+  <si>
+    <t>88.0396;3.4071;93.1037;0.080798;110.0619;5.7447;127.1344;0.12015;134.0744;0.19854;136.0816;0.30207;137.0899;0.60521;139.1754;0.12407;146.0311;0.40263;152.2021;0.17395;153.9993;100;157.0176;0.091134;161.1019;0.41306;163.0066;30.3735;164.0456;0.44737;181.0633;4.8889;207.1279;5.3484;208.1835;0.97415</t>
+  </si>
+  <si>
+    <t>81.0466;14.4313;93.0458;11.1424;110.0725;100;154.0623;79.2904;163.1012;11.0116;225.0196;17.7101;225.0988;72.2949</t>
+  </si>
+  <si>
+    <t>72.0241;13.0022;73.0025;1.0551;90.0121;2.6469;91.0147;1.3154;96.5685;0.26761;99.5668;0.18403;105.3787;15.1373;109.9533;14.4972;138.074;3.4521;152.007;21.2373;153.3394;0.15114;156.056;100;157.1546;1.0016;180.0829;51.8506;181.08;0.31604;182.1525;7.065;192.0567;1.5501;198.0437;62.2163;199.0186;0.56215;210.1292;3.288</t>
+  </si>
+  <si>
+    <t>82.924;0.34594;95.0399;3.2904;109.9994;100;110.8359;0.088213;112.1104;0.58588;138.0371;0.79941;139.0078;0.084245;147.1679;0.081572;156.067;0.070621</t>
+  </si>
+  <si>
+    <t>71.9939;13.1679;73.0595;1.0021;90.1059;2.3982;90.9925;1.49;105.3428;17.1194;106.2214;0.84576;110.0034;13.7967;134.296;0.56504;138.0382;1.8639;152.0647;19.1299;154.072;0.23069;156.1239;100;157.1071;3.1267;180.074;52.1143;181.1599;3.3209;182.0653;5.751;198.0679;73.5813;199.1559;2.7398;210.25;1.0584</t>
+  </si>
+  <si>
+    <t>83.05;0.13895;90.0507;0.06946;93.0486;0.12041;110.0011;13.7303;137.9816;4.7319;152.182;0.24491;154.2012;0.42547;156.0725;9.0137;164.1878;0.17161;180.0774;10.0342;181.1244;1.9933;182.1903;0.40168;192.1177;2.1867;198.2188;1.0049;209.1038;21.7744;210.0672;100</t>
+  </si>
+  <si>
+    <t>110.0739;25.4562;156.0802;43.5192;210.0928;9.5185;227.1144;100</t>
+  </si>
+  <si>
+    <t>83.0611;12.8332;93.0459;10.7263;95.0616;11.0375;110.0721;100;122.0726;13.1445;156.0779;32.091;164.0833;10.4908;181.1098;7.7095;210.0882;20.7662;227.1144;14.8923</t>
+  </si>
+  <si>
+    <t>109.0506;0.001001;119.0351;0.016016;135.6019;0.001001;135.9067;0.001001;135.9785;0.002002;136.01;0.001001;136.0336;0.003003;136.0348;0.001001;136.0372;0.001001;136.0417;0.001001;136.0444;0.001001;136.0459;0.001001;136.0477;0.001001;136.0489;0.001001;136.0501;0.001001;136.0513;0.001001;136.0537;0.004004;136.0549;0.002002;136.0567;0.006006;136.0588;0.008008;136.0597;0.003003;136.0612;1;136.0633;0.008008;136.0642;0.008008;136.0666;0.007007;136.0678;0.003003;136.0693;0.004004;136.0708;0.001001;136.0714;0.001001;136.072;0.001001;136.0732;0.001001;136.0744;0.001001;136.0753;0.001001;136.0762;0.001001;136.078;0.001001;136.0792;0.001001;136.0804;0.001001;136.0822;0.001001;136.0852;0.001001;136.0876;0.001001;136.0891;0.003003;136.0954;0.001001;136.1131;0.001001;136.1443;0.002002;136.2163;0.001001;136.5228;0.001001;137.0453;0.022022;137.0586;0.012012;137.0641;0.046046;149.0229;0.001001;151.0606;0.001001;152.0562;0.008008;158.0022;0.001001;160.061;0.001001;171.1487;0.005005;174.1272;0.003003;182.9848;0.001001;187.1251;0.001001;194.117;0.001001;224.1274;0.002002;272.1002;0.012012;287.1089;0.001001;306.2017;0.001001;391.2829;0.004004;392.2848;0.001001;526.3367;0.007007;527.3394;0.001001</t>
+  </si>
+  <si>
+    <t>119.0353;0.014014;135.6025;0.001001;135.91;0.001001;135.9788;0.001001;136.0112;0.001001;136.0339;0.004004;136.0417;0.001001;136.0426;0.001001;136.0453;0.001001;136.0465;0.001001;136.0477;0.002002;136.0495;0.001001;136.0513;0.002002;136.0531;0.001001;136.054;0.003003;136.0564;0.006006;136.0591;0.014014;136.0618;1;136.0639;0.013013;136.0645;0.013013;136.0669;0.007007;136.069;0.002002;136.0699;0.002002;136.0717;0.002002;136.0735;0.001001;136.0753;0.002002;136.0765;0.001001;136.0777;0.001001;136.0786;0.001001;136.0795;0.001001;136.0813;0.001001;136.0837;0.001001;136.0891;0.004004;136.1122;0.001001;136.1446;0.002002;136.2136;0.001001;136.5231;0.001001;137.0453;0.003003;137.0589;0.013013;137.062;0.001001;137.0644;0.048048;137.0668;0.001001;137.0674;0.001001;151.0613;0.001001;158.0029;0.001001;163.0611;0.001001;171.1491;0.007007;172.9767;0.001001;174.1276;0.003003;182.9848;0.001001;187.1261;0.001001;194.1175;0.009009;199.1798;0.001001;224.128;0.001001;306.2027;0.002002;348.0605;0.001001;348.0703;0.092092;348.0789;0.001001;348.0813;0.001001;349.066;0.001001;349.0734;0.007007;350.0733;0.001001;391.2829;0.003003;392.2863;0.001001;483.1234;0.002002;526.3367;0.004004;527.3394;0.001001;695.1319;0.004004;696.1369;0.001001;1042.1963;0.001001</t>
+  </si>
+  <si>
+    <t>93.965;0.21021;95.087;0.23323;112.0196;0.046046;119.0712;1;120.0677;0.25626;137.0681;0.04004</t>
+  </si>
+  <si>
+    <t>92.0255;0.067067;107.0359;0.26827;134.0467;1</t>
+  </si>
+  <si>
+    <t>64.0102;0.069069;65.0154;0.37738;68.027;0.083083;90.0129;0.089089;92.0258;0.74775;106.0312;0.064064;107.0373;1;134.0467;0.78378</t>
+  </si>
+  <si>
+    <t>92.0255;6.6857;107.0359;26.798;134.0467;100</t>
+  </si>
+  <si>
+    <t>64.0102;1.753;65.0154;9.576;68.027;2.113;90.0129;2.272;92.0258;18.98;106.0312;1.636;107.0373;25.38;134.0467;19.89</t>
+  </si>
+  <si>
+    <t>93.965;21.0387;95.087;23.3153;112.0196;4.6431;119.0712;100;120.0677;25.6644;137.0681;4.0299</t>
+  </si>
+  <si>
+    <t>58.067;0.076076;59.0751;0.046046;118.0868;1</t>
+  </si>
+  <si>
+    <t>58.0662;1;59.0743;0.30731;118.0868;0.82983</t>
+  </si>
+  <si>
+    <t>58.067;7.6454;59.0751;4.5854;118.0868;100</t>
+  </si>
+  <si>
+    <t>58.0662;45.06;59.0743;13.83;118.0868;37.37</t>
+  </si>
+  <si>
+    <t>130.0495;0.003003;136.0582;0.001001;136.0615;0.034034;137.0647;0.001001;137.132;0.001001;141.946;0.001001;149.0232;0.001001;152.024;0.001001;152.0473;0.001001;152.0505;0.001001;152.0519;0.001001;152.0534;0.002002;152.0565;0.24725;152.0587;0.002002;152.0594;0.002002;152.0612;0.001001;152.0622;0.001001;152.0661;0.001001;152.07;0.005005;152.0891;0.001001;153.0406;0.004004;153.0534;0.001001;153.0599;0.01001;155.1429;0.001001;163.1323;0.001001;171.1491;0.007007;174.1276;0.002002;177.0327;0.001001;179.0478;0.001001;181.0492;0.005005;182.9853;0.001001;187.1261;0.002002;190.989;0.001001;198.0274;0.001001;198.0626;0.001001;198.0669;0.001001;198.0695;0.001001;198.0711;0.002002;198.0732;0.002002;198.0758;0.32132;198.0805;0.002002;198.0832;0.001001;198.0842;0.001001;198.0858;0.001001;198.0895;0.001001;198.1243;0.001001;199.079;0.026026;199.1798;0.001001;200.0797;0.001001;207.024;0.001001;207.0268;0.001001;210.0759;0.001001;221.1494;0.001001;222.1123;0.011011;223.0632;0.008008;223.1155;0.001001;224.0627;0.001001;224.128;0.037037;225.1308;0.002002;231.0426;0.001001;242.5618;0.001001;275.5665;0.002002;278.5719;0.003003;279.1586;0.001001;282.2212;0.001001;298.5687;0.001001;303.1062;0.001001;305.5288;0.001001;306.5613;0.001001;306.8028;0.001001;306.9094;0.001001;306.9906;0.003003;307.0363;0.001001;307.0394;0.001001;307.0496;0.001001;307.0577;0.002002;307.0658;0.004004;307.0699;0.002002;307.0739;0.006006;307.0841;0.96296;307.0902;0.005005;307.0922;0.006006;307.0973;0.003003;307.0994;0.003003;307.1024;0.003003;307.1055;0.001001;307.1075;0.001001;307.1105;0.002002;307.1156;0.001001;307.1217;0.001001;307.1258;0.001001;307.1299;0.001001;307.1776;0.003003;307.258;0.001001;307.3648;0.001001;307.4911;0.001001;307.5665;0.001001;307.5726;0.001001;307.5746;0.001001;307.5848;0.26326;307.5909;0.002002;307.593;0.002002;307.5981;0.001001;307.6011;0.001001;307.6062;0.001001;307.6786;0.001001;308.0827;0.13013;308.0908;0.001001;308.099;0.001001;308.5817;0.015015;308.5878;0.001001;308.6503;0.001001;309.083;0.001001;334.0416;0.001001;339.0655;0.001001;346.1939;0.001001;347.4407;0.001001;347.7308;0.001001;347.8594;0.001001;347.9575;0.003003;348.0053;0.001001;348.0127;0.001001;348.0163;0.001001;348.0298;0.001001;348.0347;0.001001;348.0384;0.002002;348.0482;0.003003;348.0531;0.002002;348.0556;0.003003;348.058;0.005005;348.0617;0.001001;348.0703;1;348.0777;0.006006;348.0801;0.006006;348.0838;0.002002;348.0862;0.003003;348.0899;0.003003;348.0936;0.002002;348.0961;0.001001;348.1034;0.002002;348.1083;0.001001;348.1157;0.001001;348.1206;0.001001;348.1255;0.001001;348.128;0.001001;348.1832;0.003003;348.2801;0.001001;348.4091;0.001001;348.7016;0.001001;348.7496;0.001001;349.061;0.001001;349.0734;0.10611;349.1239;0.003003;349.9608;0.001001;350.0733;0.006006;350.1278;0.001001;355.0725;0.001001;362.085;0.001001;391.2829;0.006006;392.2863;0.001001;484.1158;0.002002;499.1168;0.008008;500.1209;0.001001;502.221;0.001001;556.1353;0.001001;560.0551;0.001001;588.352;0.001001;612.8962;0.001001;613.1083;0.001001;613.1198;0.001001;613.1313;0.002002;613.1599;0.33834;613.1771;0.002002;613.1829;0.001001;613.1915;0.001001;613.1972;0.001001;613.203;0.001001;613.4239;0.001001;614.162;0.078078;615.1522;0.018018;616.1563;0.004004;695.1319;0.018018;696.1369;0.002002;697.1371;0.001001;738.3467;0.001001;786.6905;0.005005;787.1909;0.003003;787.6876;0.001001;919.2316;0.007007;919.7372;0.007007;920.2379;0.003003;920.739;0.001001;921.2353;0.001001;921.7372;0.001001;960.2192;0.025025;960.7253;0.004004;961.2261;0.01001;961.7216;0.001001;962.2288;0.002002;1001.2103;0.001001;1001.7132;0.001001;1022.2588;0.001001;1042.1963;0.002002;1043.1948;0.001001;1059.2566;0.001001;1092.7659;0.005005;1093.2642;0.005005;1093.7696;0.005005;1094.2686;0.001001;1094.761;0.001001;1095.2675;0.001001;1095.7675;0.001001;1133.7519;0.002002;1134.2568;0.002002;1134.7549;0.001001;1135.2605;0.001001;1136.9458;0.001001;1137.2789;0.001001;1137.6195;0.001001;1191.8092;0.001001;1225.3107;0.003003;1225.8132;0.002002;1226.3159;0.003003;1226.8109;0.001001;1227.3061;0.001001;1253.3106;0.001001;1253.9813;0.001001;1254.3001;0.001001;1266.3004;0.003003;1266.8027;0.003003;1267.3053;0.003003;1267.7997;0.002002;1268.3029;0.001001;1307.2901;0.002002;1307.7813;0.001001;1308.2906;0.002002;1342.3343;0.001001;1368.6606;0.001001;1368.9954;0.001001;1398.8472;0.001001;1399.3514;0.001001;1399.8459;0.001001;1400.3505;0.001001;1400.8357;0.001001;1439.8281;0.001001;1440.3339;0.001001;1440.8296;0.001001;1441.8322;0.001001;1485.0225;0.001001</t>
+  </si>
+  <si>
+    <t>127.0233;0.001001;130.0929;0.75676;131.1612;0.028028;143.9153;0.002002;149.0912;0.001001;162.1169;0.02002;177.1242;0.009009;178.9018;0.017017;191.3205;0.004004;199.1908;0.01001;209.0196;0.006006;211.1237;0.009009;215.0482;0.003003;216.3421;0.001001;219.6343;0.011011;224.6858;0.004004;229.222;0.002002;231.1347;0.027027;231.9268;0.001001;232.9228;0.005005;234.0895;0.004004;235.2574;0.009009;238.1393;0.014014;242.6279;0.24424;243.2363;0.089089;245.2065;0.004004;246.5023;0.016016;247.1813;0.001001;252.6116;0.004004;253.2235;0.001001;256.1463;0.001001;257.1635;0.017017;258.1801;0.001001;260.6276;0.028028;261.315;0.004004;262.1158;0.004004;263.4603;0.002002;265.2814;0.007007;266.0904;0.001001;266.8207;0.003003;269.5674;0.24224;270.2487;0.032032;271.2513;0.002002;274.3643;0.001001;275.5626;0.31331;276.2877;0.036036;277.434;0.005005;278.3113;0.002002;279.1736;0.002002;280.0804;0.002002;284.1974;0.001001;288.3268;0.005005;289.1642;0.002002;290.0743;0.005005;291.2597;0.001001;298.5695;0.68468;299.2609;0.058058;308.0765;0.001001;322.3194;0.001001;337.2779;0.009009;338.1308;0.003003;339.912;0.004004;355.1736;1;356.1731;0.086086;363.9594;0.005005;365.3393;0.006006;381.1599;0.037037;382.275;0.015015;404.0603;0.002002;409.2166;0.14214;410.2389;0.013013;447.4021;0.004004;466.1856;0.022022;467.1778;0.004004;475.3458;0.001001;484.1849;0.48148;485.2762;0.051051;520.3584;0.006006;538.2421;0.12713;539.2702;0.012012</t>
+  </si>
+  <si>
+    <t>109.1005;0.001001;119.0372;0.059059;136.0284;1;137.0919;0.002002;250.2114;0.003003</t>
+  </si>
+  <si>
+    <t>177.2126;0.001001;181.216;0.001001;185.0822;0.001001;199.1089;0.001001;209.0233;0.009009;211.1267;0.012012;231.2498;0.008008;235.1682;0.006006;256.3174;0.002002;257.2527;0.001001;262.143;0.002002;280.1777;0.001001;288.273;0.004004;298.2391;0.002002;320.1148;0.001001;322.1875;0.003003;337.2275;0.006006;338.151;0.001001;340.1581;0.002002;355.1479;0.96897;391.283;0.003003;409.166;0.053053;421.2112;0.002002;466.2176;0.074074;484.132;1;484.7725;0.004004;520.3344;0.004004;538.3328;0.03003;550.2903;0.001001;577.1907;0.002002;595.2221;0.22723;596.0662;0.001001</t>
+  </si>
+  <si>
+    <t>100.1118;0.002002;101.0957;0.001001;136.0576;0.002002;136.0594;0.002002;136.0615;0.10811;136.0636;0.002002;136.0645;0.002002;136.0663;0.001001;137.0586;0.001001;137.0647;0.004004;137.132;0.002002;141.9585;0.003003;149.0232;0.002002;153.0756;0.001001;155.1429;0.003003;158.0026;0.001001;158.096;0.001001;163.1327;0.004004;170.0963;0.001001;171.1491;0.025025;172.152;0.001001;174.1276;0.01001;179.0632;0.002002;182.9848;0.002002;186.1849;0.001001;187.1261;0.009009;199.1804;0.003003;208.1902;0.001001;214.0255;0.001001;220.112;0.001001;222.0117;0.001001;223.0632;0.005005;224.128;0.011011;225.1308;0.001001;226.0158;0.001001;233.174;0.001001;234.5384;0.001001;279.1586;0.001001;282.2212;0.001001;346.1939;0.001001;347.7308;0.001001;347.8631;0.001001;347.9575;0.003003;347.9759;0.001001;347.9832;0.001001;347.9955;0.001001;348.0004;0.001001;348.0102;0.001001;348.0151;0.001001;348.0225;0.001001;348.0274;0.001001;348.0347;0.002002;348.0396;0.002002;348.0433;0.002002;348.0507;0.005005;348.0605;0.012012;348.0703;1;348.0777;0.012012;348.0813;0.009009;348.0899;0.005005;348.0936;0.002002;348.0985;0.002002;348.1034;0.002002;348.1083;0.001001;348.1108;0.001001;348.1157;0.001001;348.1206;0.001001;348.123;0.001001;348.128;0.001001;348.1378;0.001001;348.1427;0.001001;348.1476;0.001001;348.1549;0.001001;348.1832;0.003003;348.2777;0.001001;348.4091;0.001001;348.6942;0.001001;349.0536;0.001001;349.0623;0.001001;349.0721;0.12312;349.0807;0.001001;349.0832;0.001001;349.962;0.001001;350.0746;0.014014;351.0764;0.001001;359.0537;0.001001;360.0479;0.001001;370.0269;0.001001;370.0512;0.001001;374.5258;0.001001;375.0287;0.002002;391.2829;0.013013;392.2863;0.002002;426.3567;0.001001;436.3395;0.001001;526.3367;0.002002;533.5792;0.001001;543.5578;0.001001;695.1042;0.001001;695.1319;0.075075;695.1561;0.001001;695.1665;0.001001;696.1369;0.013013;697.1371;0.002002;707.1099;0.001001;738.3467;0.001001;749.0497;0.001001;1042.1963;0.015015;1042.6985;0.002002;1043.2011;0.005005;1044.2011;0.001001;1215.7265;0.001001;1216.2311;0.001001;1216.728;0.001001;1389.2617;0.003003;1389.7606;0.001001;1390.2598;0.001001</t>
+  </si>
+  <si>
+    <t>57.8693;0.14414;72.1243;0.10811;87.9758;0.50951;89.6465;0.15115;91.0191;0.3023;93.881;0.25225;107.2492;0.17417;108.0735;0.40641;115.6934;0.34134;117.0647;0.24525;117.9873;1;119.0536;0.8969;124.4474;0.34134;136.093;0.47247</t>
+  </si>
+  <si>
+    <t>108.9954;0.001001;119.0666;0.068068;135.9919;1;136.9661;0.003003;250.2034;0.003003</t>
+  </si>
+  <si>
+    <t>109.0134;0.002002;118.9953;0.058058;120.1135;0.004004;135.9731;1;136.956;0.082082;250.2528;0.004004;330.0634;0.001001</t>
+  </si>
+  <si>
+    <t>107.0364;0.002002;112.6764;0.001001;128.0352;0.009009;134.0413;0.001001;134.0425;0.001001;134.0448;0.002002;134.0474;0.065065;134.0498;0.002002;134.0521;0.001001;135.0449;0.001001;135.0503;0.002002;138.9801;0.007007;141.0668;0.001001;143.0436;0.001001;143.0461;0.019019;145.0615;0.001001;146.0456;0.002002;150.0418;0.001001;150.9799;0.015015;153.0667;0.002002;155.0825;0.001001;160.0073;0.004004;162.9799;0.001001;166.0984;0.001001;167.046;0.001001;169.0616;0.002002;175.018;0.001001;177.0335;0.003003;179.046;0.002002;181.0617;0.001001;184.1086;0.001001;185.0562;0.001001;192.9904;0.008008;196.0612;0.003003;197.0561;0.003003;198.0882;0.001001;199.0721;0.001001;203.0491;0.003003;210.0879;0.005005;210.9911;0.001001;210.9964;0.001001;211.001;0.022022;212.004;0.001001;226.0827;0.001001;228.0987;0.002002;242.078;0.001001;254.0778;0.008008;260.0879;0.001001;272.0752;0.001001;272.082;0.001001;272.0845;0.001001;272.0888;0.066066;272.0956;0.001001;272.1032;0.001001;273.0913;0.006006;274.0924;0.001001;276.0178;0.001001;280.8595;0.001001;288.0659;0.004004;294.0281;0.001001;304.0523;0.001001;304.0603;0.027027;305.0635;0.002002;305.9827;0.001001;306.0515;0.001001;306.0606;0.003003;306.0686;0.005005;306.0767;0.24024;306.0848;0.005005;306.0939;0.003003;306.098;0.001001;306.102;0.001001;306.1061;0.001001;306.1698;0.001001;307.0726;0.001001;307.0798;0.021021;308.0714;0.008008;308.0795;0.001001;309.075;0.001001;338.0485;0.016016;339.0524;0.001001;340.0441;0.001001;345.719;0.002002;345.9425;0.003003;345.9559;0.001001;345.9729;0.001001;345.9827;0.001001;345.9863;0.001001;345.9924;0.001001;345.9973;0.001001;346.0046;0.001001;346.0082;0.001001;346.0143;0.001001;346.0167;0.001001;346.024;0.004004;346.035;0.011011;346.0447;0.02002;346.0544;1;346.0641;0.019019;346.0751;0.011011;346.08;0.003003;346.086;0.003003;346.0897;0.002002;346.097;0.002002;346.1006;0.001001;346.1031;0.001001;346.1067;0.001001;346.1104;0.001001;346.1152;0.001001;346.1189;0.001001;346.1237;0.001001;346.1347;0.001001;346.1384;0.001001;346.1529;0.001001;346.1676;0.003003;346.3916;0.002002;347.0392;0.001001;347.0478;0.002002;347.0576;0.097097;347.0673;0.002002;347.0783;0.001001;348.0589;0.008008;349.0622;0.001001;360.0699;0.001001;378.896;0.003003;426.0212;0.004004;444.0227;0.014014;445.0267;0.001001;445.9807;0.001001;480.9815;0.002002;482.1015;0.002002;489.9927;0.001001;497.1063;0.001001;504.9391;0.012012;505.9439;0.001001;513.9522;0.007007;514.9552;0.001001;522.951;0.003003;529.9454;0.006006;530.9495;0.001001;531.9633;0.001001;543.0876;0.001001;543.1044;0.001001;543.1235;0.063063;543.1426;0.001001;543.1666;0.001001;544.1269;0.01001;545.1306;0.001001;547.9574;0.002002;554.1232;0.002002;559.9577;0.001001;593.1364;0.002002;610.3551;0.001001;610.8797;0.002002;610.9538;0.001001;610.9995;0.001001;611.0109;0.001001;611.028;0.001001;611.0337;0.001001;611.048;0.001001;611.0566;0.001001;611.0737;0.002002;611.0994;0.007007;611.1222;0.013013;611.145;0.87087;611.1679;0.012012;611.1936;0.007007;611.205;0.002002;611.2164;0.002002;611.2278;0.001001;611.245;0.001001;611.2507;0.001001;611.2735;0.001001;611.3078;0.001001;611.4077;0.002002;611.8821;0.001001;611.9365;0.001001;612.0738;0.001001;612.1024;0.002002;612.1253;0.003003;612.1482;0.22022;612.1711;0.003003;612.1968;0.002002;612.4115;0.001001;613.1165;0.001001;613.1394;0.055055;613.1509;0.011011;613.1595;0.002002;614.1417;0.008008;614.1532;0.001001;615.1321;0.001001;615.1436;0.001001;633.126;0.003003;653.14;0.001001;665.0638;0.001001;692.7973;0.001001;693.0316;0.001001;693.0627;0.004004;693.0902;0.008008;693.1006;0.006006;693.1178;0.53053;693.1454;0.007007;693.1764;0.004004;693.1902;0.001001;693.2006;0.001001;693.2178;0.001001;693.2385;0.001001;693.4351;0.001001;694.0669;0.001001;694.0945;0.002002;694.1221;0.11912;694.1498;0.001001;694.1809;0.001001;695.1217;0.017017;696.1269;0.002002;702.0075;0.001001;707.1344;0.001001;709.1102;0.009009;710.1138;0.001001;711.1051;0.001001;715.0986;0.002002;717.0753;0.001001;737.0367;0.001001;852.0045;0.003003;853.0062;0.001001;861.0167;0.002002;877.007;0.001001;890.1864;0.002002;958.0664;0.001001;958.1168;0.002002;958.1617;0.004004;958.1785;0.002002;958.2065;0.26426;958.2513;0.003003;958.285;0.001001;958.3018;0.002002;958.3242;0.001001;958.7223;0.001001;959.1206;0.001001;959.1655;0.001001;959.1823;0.001001;959.2104;0.088088;959.2553;0.001001;959.3058;0.001001;960.2102;0.015015;961.206;0.004004;962.209;0.001001;980.192;0.001001;999.6983;0.001001;1040.1822;0.029029;1041.1843;0.009009;1042.1816;0.002002;1090.759;0.001001;1117.0892;0.001001;1126.1091;0.001001;1131.7346;0.002002;1132.2383;0.002002;1132.7423;0.001001;1133.2539;0.001001;1142.0913;0.001001;1172.7229;0.001001;1173.2238;0.001001;1199.0541;0.001001;1223.2938;0.002002;1224.3049;0.001001;1264.7777;0.001001;1265.2792;0.001001;1305.2663;0.009009;1305.7654;0.001001;1306.2736;0.006006;1306.7822;0.001001;1307.2732;0.002002;1308.265;0.001001;1387.2507;0.003003;1388.2469;0.001001;1389.254;0.001001;1437.8115;0.001001;1438.3061;0.001001;1438.8318;0.001001;1478.7871;0.001001;1479.2922;0.001001;1479.8083;0.001001</t>
+  </si>
+  <si>
+    <t>134.0199;0.014014;138.8643;0.017017;151.0103;0.12513;175.1155;0.003003;192.9996;0.063063;210.9611;1</t>
+  </si>
+  <si>
+    <t>177.1261;0.003003;179.0811;0.034034;185.0484;0.002002;192.1729;0.003003;193.0073;0.001001;197.188;0.006006;210.2406;0.032032;213.1394;0.001001;226.1801;0.002002;228.2151;0.001001;236.2177;0.001001;242.2623;0.002002;252.2125;0.003003;254.1804;0.14414;262.3164;0.001001;263.0907;0.001001;272.1571;0.39239;286.2136;0.007007;288.1422;0.053053;304.1935;0.14214;306.1412;1;320.1056;0.002002;338.1055;0.44344;353.2388;0.003003;464.1958;0.016016;482.1046;0.40941;482.7614;0.001001;575.1926;0.005005;593.1372;0.18819;593.8993;0.001001</t>
+  </si>
+  <si>
+    <t>211.1148;0.005005;328.1527;0.005005;346.041;1;346.6807;0.001001;426.1268;0.086086</t>
+  </si>
+  <si>
+    <t>107.0364;0.004004;118.8185;0.001001;134.0416;0.002002;134.0448;0.003003;134.0472;0.085085;134.0498;0.002002;134.0521;0.001001;134.0741;0.001001;135.044;0.001001;135.0503;0.003003;138.9801;0.008008;150.9771;0.001001;150.9799;0.018018;150.9824;0.001001;175.0245;0.003003;191.019;0.002002;192.9904;0.009009;210.9964;0.001001;211.001;0.03003;211.0056;0.001001;212.004;0.001001;345.719;0.002002;345.9049;0.001001;345.9365;0.001001;345.9425;0.004004;345.9535;0.001001;345.9584;0.001001;345.9632;0.001001;345.9681;0.001001;345.9705;0.001001;345.9851;0.001001;345.9924;0.001001;345.9997;0.001001;346.0118;0.002002;346.0167;0.002002;346.024;0.004004;346.035;0.007007;346.0447;0.02002;346.0544;1;346.0654;0.018018;346.0751;0.008008;346.0836;0.003003;346.0873;0.003003;346.0909;0.001001;346.0946;0.001001;346.097;0.001001;346.0994;0.001001;346.1092;0.001001;346.1152;0.001001;346.1189;0.001001;346.1225;0.001001;346.1262;0.001001;346.1432;0.001001;346.1481;0.001001;346.1542;0.001001;346.1578;0.001001;346.1663;0.004004;346.1749;0.001001;346.3916;0.001001;347.0368;0.001001;347.0478;0.002002;347.0576;0.098098;348.0589;0.008008;349.0609;0.001001;360.0699;0.002002;426.0212;0.006006;444.0227;0.004004;479.9409;0.001001;480.0025;0.001001;498.0688;0.001001;504.9391;0.001001;522.0867;0.002002;529.9454;0.001001;567.1612;0.001001;569.1749;0.001001;692.1638;0.001001;692.8007;0.002002;692.9213;0.001001;692.942;0.001001;692.9627;0.001001;692.9834;0.001001;692.9972;0.001001;693.0109;0.001001;693.0178;0.001001;693.0316;0.002002;693.0627;0.004004;693.0902;0.012012;693.1178;0.80681;693.1488;0.01001;693.1764;0.005005;693.1902;0.001001;693.2006;0.002002;693.2109;0.002002;693.2212;0.001001;693.2316;0.001001;693.2385;0.001001;693.2454;0.001001;693.273;0.001001;693.3213;0.001001;693.3695;0.001001;693.4351;0.002002;693.8044;0.001001;694.06;0.001001;694.0738;0.001001;694.091;0.003003;694.1014;0.001001;694.1187;0.1952;694.1498;0.003003;694.1809;0.001001;695.1217;0.034034;696.1269;0.003003;707.1308;0.002002;715.0986;0.006006;716.1004;0.001001;737.0367;0.002002;746.0284;0.001001;747.0381;0.001001;877.007;0.001001;916.2407;0.001001;1040.0744;0.001001;1040.1315;0.002002;1040.1822;0.2032;1040.2392;0.002002;1040.2899;0.001001;1041.1272;0.001001;1041.1843;0.058058;1041.2224;0.001001;1041.2415;0.001001;1042.1879;0.01001;1043.1866;0.002002;1054.1965;0.001001;1062.1631;0.001001;1213.715;0.002002;1214.2184;0.002002;1214.7142;0.001001;1387.2409;0.014014;1387.2995;0.001001;1387.7389;0.003003;1388.2469;0.009009;1388.7552;0.001001;1389.254;0.003003;1390.2524;0.001001</t>
+  </si>
+  <si>
+    <t>122.9577;0.001001;134.0146;0.013013;138.9515;0.019019;150.9498;0.11411;192.9332;0.064064;193.5348;0.002002;211.0139;1;248.1697;0.006006</t>
+  </si>
+  <si>
+    <t>211.1263;0.005005;328.196;0.005005;346.0907;1;426.0713;0.083083</t>
+  </si>
+  <si>
+    <t>78.9598;1;96.9698;0.37938;134.047;0.2983;346.0553;0.66767</t>
+  </si>
+  <si>
+    <t>134.0199;1.4047;138.8643;1.6561;151.0103;12.4703;175.1155;0.32852;192.9996;6.302;210.9611;100</t>
+  </si>
+  <si>
+    <t>211.1148;0.52716;328.1527;0.50816;346.041;100;346.6807;0.1188;426.1268;8.5739</t>
+  </si>
+  <si>
+    <t>122.9577;0.074379;134.0146;1.3171;138.9515;1.9135;150.9498;11.4558;192.9332;6.4314;193.5348;0.18807;211.0139;100;248.1697;0.62908</t>
+  </si>
+  <si>
+    <t>211.1263;0.48476;328.196;0.51294;346.0907;100;426.0713;8.2841</t>
+  </si>
+  <si>
+    <t>78.9598;100;96.9698;37.8919;134.047;29.8603;346.0553;66.7679</t>
+  </si>
+  <si>
+    <t>109.1005;0.10551;119.0372;5.949;136.0284;100;137.0919;0.15768;250.2114;0.33358</t>
+  </si>
+  <si>
+    <t>57.8693;3.4729;72.1243;2.6033;87.9758;12.2769;89.6465;3.6445;91.0191;7.2956;93.881;6.0853;107.2492;4.1872;108.0735;9.7877;115.6934;8.2263;117.0647;5.9089;117.9873;24.0954;119.0536;21.6223;124.4474;8.2244;136.093;11.3757</t>
+  </si>
+  <si>
+    <t>108.9954;0.14732;119.0666;6.8084;135.9919;100;136.9661;0.27174;250.2034;0.30463</t>
+  </si>
+  <si>
+    <t>109.0134;0.1505;118.9953;5.8116;120.1135;0.42361;135.9731;100;136.956;8.2056;250.2528;0.37831;330.0634;0.073459</t>
+  </si>
+  <si>
+    <t>136.0585;0.002002;136.0615;0.043043;136.063;0.001001;136.0642;0.001001;137.0647;0.001001;139.0498;0.001001;171.1487;0.005005;172.9767;0.001001;174.1276;0.002002;179.0632;0.001001;182.9848;0.002002;187.1256;0.001001;194.117;0.008008;199.1798;0.001001;222.1123;0.001001;224.128;0.003003;242.5618;0.005005;243.0635;0.001001;245.0765;0.003003;266.8351;0.001001;267.6868;0.001001;267.8747;0.001001;267.965;0.001001;268.0271;0.003003;268.0545;0.001001;268.0636;0.001001;268.0661;0.001001;268.0735;0.001001;268.076;0.001001;268.0793;0.001001;268.0818;0.001001;268.0843;0.001001;268.0868;0.002002;268.0885;0.001001;268.0909;0.003003;268.0926;0.003003;268.0967;0.011011;268.1042;1;268.1108;0.011011;268.1183;0.004004;268.12;0.001001;268.1233;0.001001;268.1249;0.002002;268.1299;0.001001;268.1332;0.001001;268.1365;0.001001;268.1399;0.001001;268.1432;0.001001;268.1515;0.001001;268.1548;0.001001;268.1797;0.003003;268.2436;0.001001;268.3332;0.001001;268.5226;0.001001;269.0987;0.001001;269.1012;0.001001;269.1062;0.12513;269.1103;0.001001;269.1128;0.001001;269.3815;0.001001;270.1029;0.001001;270.1062;0.003003;270.1087;0.001001;308.0816;0.001001;308.0847;0.001001;308.0908;0.1041;308.0959;0.001001;308.1;0.001001;309.0933;0.009009;310.0861;0.003003;391.2829;0.004004;392.2848;0.001001;484.1138;0.001001;575.1855;0.001001;615.1724;0.001001;658.3798;0.003003;659.3828;0.001001</t>
+  </si>
+  <si>
+    <t>119.1007;0.001001;136.0241;0.83884;136.9659;1;202.2043;0.001001;251.1233;0.001001</t>
+  </si>
+  <si>
+    <t>119.0498;0.001001;136.0259;1;136.8551;0.001001</t>
+  </si>
+  <si>
+    <t>107.0358;0.12813;134.0467;1;266.089;0.15916</t>
+  </si>
+  <si>
+    <t>119.035;0.078078;136.0616;1;268.1046;0.10611</t>
+  </si>
+  <si>
+    <t>92.0254;0.12157;107.0365;0.4947;134.0472;100;266.0894;15.1136</t>
+  </si>
+  <si>
+    <t>92.0254;0.29692;107.0363;0.97573;134.0472;100;266.0894;3.0079</t>
+  </si>
+  <si>
+    <t>92.0255;1.1176;107.0363;3.6276;134.0472;100</t>
+  </si>
+  <si>
+    <t>65.0145;0.65331;92.0254;3.83;107.0363;16.1238;134.0472;100</t>
+  </si>
+  <si>
+    <t>65.0145;1.616;68.0255;0.51227;79.0176;0.13257;80.0254;0.83272;92.0255;12.8738;107.0363;44.506;117.0206;0.14336;133.0396;0.19335;134.0472;100</t>
+  </si>
+  <si>
+    <t>64.0065;0.16768;65.0145;6.4389;66.0097;0.27219;68.0254;2.4858;80.0255;1.5166;92.0255;33.2023;106.0285;0.29058;107.0363;88.119;133.0395;0.36709;134.0472;100</t>
+  </si>
+  <si>
+    <t>107.0358;12.79;134.0467;100;266.089;15.9287</t>
+  </si>
+  <si>
+    <t>precursor_mz</t>
+  </si>
+  <si>
     <t>228.0979</t>
   </si>
   <si>
@@ -498,273 +802,6 @@
     <t>negative</t>
   </si>
   <si>
-    <t>peak_counter</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>814</t>
-  </si>
-  <si>
-    <t>1000</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>228</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>137</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>188</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>325</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>722</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>249</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>282</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>ms2_peak</t>
   </si>
   <si>
@@ -1063,16 +1100,12 @@
   </si>
   <si>
     <t>107.0358;12.79;134.0467;100;266.089;15.9287</t>
-  </si>
-  <si>
-    <t>precursor_mz</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1392,28 +1425,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.140625" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
     <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="5" width="5801.7109375" customWidth="1"/>
+    <col min="3" max="5" width="5801.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>200</v>
       </c>
       <c r="B1" t="s">
-        <v>127</v>
+        <v>228</v>
       </c>
       <c r="C1" t="s">
-        <v>159</v>
+        <v>260</v>
       </c>
       <c r="D1" t="s">
-        <v>248</v>
+        <v>100</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -1421,16 +1453,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>201</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>229</v>
       </c>
       <c r="C2" t="s">
-        <v>160</v>
+        <v>261</v>
       </c>
       <c r="D2" t="s">
-        <v>249</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>1</v>
@@ -1438,16 +1470,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>202</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>230</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>262</v>
       </c>
       <c r="D3" t="s">
-        <v>250</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -1455,16 +1487,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>202</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>231</v>
       </c>
       <c r="C4" t="s">
-        <v>161</v>
+        <v>263</v>
       </c>
       <c r="D4" t="s">
-        <v>251</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
@@ -1472,16 +1504,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>203</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>232</v>
       </c>
       <c r="C5" t="s">
-        <v>162</v>
+        <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>252</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
         <v>4</v>
@@ -1489,16 +1521,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>204</v>
       </c>
       <c r="B6" t="s">
-        <v>132</v>
+        <v>233</v>
       </c>
       <c r="C6" t="s">
-        <v>163</v>
+        <v>265</v>
       </c>
       <c r="D6" t="s">
-        <v>253</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -1506,16 +1538,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>205</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>233</v>
       </c>
       <c r="C7" t="s">
-        <v>164</v>
+        <v>266</v>
       </c>
       <c r="D7" t="s">
-        <v>254</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -1523,16 +1555,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>206</v>
       </c>
       <c r="B8" t="s">
-        <v>132</v>
+        <v>233</v>
       </c>
       <c r="C8" t="s">
-        <v>165</v>
+        <v>267</v>
       </c>
       <c r="D8" t="s">
-        <v>255</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -1540,16 +1572,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>206</v>
       </c>
       <c r="B9" t="s">
-        <v>132</v>
+        <v>233</v>
       </c>
       <c r="C9" t="s">
-        <v>166</v>
+        <v>268</v>
       </c>
       <c r="D9" t="s">
-        <v>256</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1557,16 +1589,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>207</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>234</v>
       </c>
       <c r="C10" t="s">
-        <v>167</v>
+        <v>269</v>
       </c>
       <c r="D10" t="s">
-        <v>257</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1574,16 +1606,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>207</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>235</v>
       </c>
       <c r="C11" t="s">
-        <v>167</v>
+        <v>270</v>
       </c>
       <c r="D11" t="s">
-        <v>258</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -1591,16 +1623,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>236</v>
       </c>
       <c r="C12" t="s">
-        <v>168</v>
+        <v>271</v>
       </c>
       <c r="D12" t="s">
-        <v>259</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -1608,16 +1640,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>208</v>
       </c>
       <c r="B13" t="s">
-        <v>135</v>
+        <v>236</v>
       </c>
       <c r="C13" t="s">
-        <v>169</v>
+        <v>272</v>
       </c>
       <c r="D13" t="s">
-        <v>260</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
         <v>12</v>
@@ -1625,16 +1657,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>209</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>237</v>
       </c>
       <c r="C14" t="s">
-        <v>170</v>
+        <v>273</v>
       </c>
       <c r="D14" t="s">
-        <v>261</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
         <v>13</v>
@@ -1642,16 +1674,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>109</v>
+        <v>210</v>
       </c>
       <c r="B15" t="s">
-        <v>137</v>
+        <v>238</v>
       </c>
       <c r="C15" t="s">
-        <v>171</v>
+        <v>274</v>
       </c>
       <c r="D15" t="s">
-        <v>262</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
@@ -1659,16 +1691,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>109</v>
+        <v>210</v>
       </c>
       <c r="B16" t="s">
-        <v>137</v>
+        <v>238</v>
       </c>
       <c r="C16" t="s">
-        <v>172</v>
+        <v>275</v>
       </c>
       <c r="D16" t="s">
-        <v>263</v>
+        <v>115</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -1676,16 +1708,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>109</v>
+        <v>210</v>
       </c>
       <c r="B17" t="s">
-        <v>137</v>
+        <v>238</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>276</v>
       </c>
       <c r="D17" t="s">
-        <v>264</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
         <v>16</v>
@@ -1693,16 +1725,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>110</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s">
-        <v>138</v>
+        <v>239</v>
       </c>
       <c r="C18" t="s">
-        <v>173</v>
+        <v>277</v>
       </c>
       <c r="D18" t="s">
-        <v>265</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
@@ -1710,16 +1742,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s">
-        <v>138</v>
+        <v>239</v>
       </c>
       <c r="C19" t="s">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="D19" t="s">
-        <v>266</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
         <v>18</v>
@@ -1727,16 +1759,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s">
-        <v>138</v>
+        <v>239</v>
       </c>
       <c r="C20" t="s">
-        <v>175</v>
+        <v>279</v>
       </c>
       <c r="D20" t="s">
-        <v>267</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -1744,16 +1776,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s">
-        <v>138</v>
+        <v>239</v>
       </c>
       <c r="C21" t="s">
-        <v>176</v>
+        <v>280</v>
       </c>
       <c r="D21" t="s">
-        <v>268</v>
+        <v>120</v>
       </c>
       <c r="E21" t="s">
         <v>20</v>
@@ -1761,16 +1793,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>110</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s">
-        <v>138</v>
+        <v>239</v>
       </c>
       <c r="C22" t="s">
-        <v>177</v>
+        <v>281</v>
       </c>
       <c r="D22" t="s">
-        <v>269</v>
+        <v>121</v>
       </c>
       <c r="E22" t="s">
         <v>21</v>
@@ -1778,16 +1810,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>110</v>
+        <v>211</v>
       </c>
       <c r="B23" t="s">
-        <v>138</v>
+        <v>239</v>
       </c>
       <c r="C23" t="s">
-        <v>178</v>
+        <v>282</v>
       </c>
       <c r="D23" t="s">
-        <v>270</v>
+        <v>122</v>
       </c>
       <c r="E23" t="s">
         <v>22</v>
@@ -1795,16 +1827,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="B24" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="C24" t="s">
-        <v>179</v>
+        <v>283</v>
       </c>
       <c r="D24" t="s">
-        <v>271</v>
+        <v>123</v>
       </c>
       <c r="E24" t="s">
         <v>23</v>
@@ -1812,16 +1844,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="B25" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="C25" t="s">
-        <v>180</v>
+        <v>284</v>
       </c>
       <c r="D25" t="s">
-        <v>272</v>
+        <v>124</v>
       </c>
       <c r="E25" t="s">
         <v>24</v>
@@ -1829,16 +1861,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="B26" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="C26" t="s">
-        <v>181</v>
+        <v>285</v>
       </c>
       <c r="D26" t="s">
-        <v>273</v>
+        <v>125</v>
       </c>
       <c r="E26" t="s">
         <v>25</v>
@@ -1846,16 +1878,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="B27" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="C27" t="s">
-        <v>182</v>
+        <v>286</v>
       </c>
       <c r="D27" t="s">
-        <v>274</v>
+        <v>126</v>
       </c>
       <c r="E27" t="s">
         <v>26</v>
@@ -1863,16 +1895,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="B28" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="C28" t="s">
-        <v>183</v>
+        <v>287</v>
       </c>
       <c r="D28" t="s">
-        <v>275</v>
+        <v>127</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -1880,16 +1912,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="B29" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="C29" t="s">
-        <v>184</v>
+        <v>288</v>
       </c>
       <c r="D29" t="s">
-        <v>276</v>
+        <v>128</v>
       </c>
       <c r="E29" t="s">
         <v>28</v>
@@ -1897,16 +1929,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="B30" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="C30" t="s">
-        <v>185</v>
+        <v>289</v>
       </c>
       <c r="D30" t="s">
-        <v>277</v>
+        <v>129</v>
       </c>
       <c r="E30" t="s">
         <v>29</v>
@@ -1914,16 +1946,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="B31" t="s">
-        <v>139</v>
+        <v>240</v>
       </c>
       <c r="C31" t="s">
-        <v>186</v>
+        <v>290</v>
       </c>
       <c r="D31" t="s">
-        <v>278</v>
+        <v>130</v>
       </c>
       <c r="E31" t="s">
         <v>30</v>
@@ -1931,16 +1963,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="B32" t="s">
-        <v>140</v>
+        <v>241</v>
       </c>
       <c r="C32" t="s">
-        <v>187</v>
+        <v>291</v>
       </c>
       <c r="D32" t="s">
-        <v>279</v>
+        <v>131</v>
       </c>
       <c r="E32" t="s">
         <v>31</v>
@@ -1948,16 +1980,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="B33" t="s">
-        <v>140</v>
+        <v>241</v>
       </c>
       <c r="C33" t="s">
-        <v>188</v>
+        <v>292</v>
       </c>
       <c r="D33" t="s">
-        <v>280</v>
+        <v>132</v>
       </c>
       <c r="E33" t="s">
         <v>32</v>
@@ -1965,16 +1997,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="B34" t="s">
-        <v>140</v>
+        <v>241</v>
       </c>
       <c r="C34" t="s">
-        <v>189</v>
+        <v>293</v>
       </c>
       <c r="D34" t="s">
-        <v>281</v>
+        <v>133</v>
       </c>
       <c r="E34" t="s">
         <v>33</v>
@@ -1982,16 +2014,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="B35" t="s">
-        <v>140</v>
+        <v>241</v>
       </c>
       <c r="C35" t="s">
-        <v>190</v>
+        <v>294</v>
       </c>
       <c r="D35" t="s">
-        <v>282</v>
+        <v>134</v>
       </c>
       <c r="E35" t="s">
         <v>34</v>
@@ -1999,16 +2031,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="B36" t="s">
-        <v>140</v>
+        <v>241</v>
       </c>
       <c r="C36" t="s">
-        <v>191</v>
+        <v>295</v>
       </c>
       <c r="D36" t="s">
-        <v>283</v>
+        <v>135</v>
       </c>
       <c r="E36" t="s">
         <v>35</v>
@@ -2016,16 +2048,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>241</v>
       </c>
       <c r="C37" t="s">
-        <v>192</v>
+        <v>296</v>
       </c>
       <c r="D37" t="s">
-        <v>284</v>
+        <v>136</v>
       </c>
       <c r="E37" t="s">
         <v>36</v>
@@ -2033,16 +2065,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>112</v>
+        <v>213</v>
       </c>
       <c r="B38" t="s">
-        <v>140</v>
+        <v>241</v>
       </c>
       <c r="C38" t="s">
-        <v>193</v>
+        <v>297</v>
       </c>
       <c r="D38" t="s">
-        <v>285</v>
+        <v>137</v>
       </c>
       <c r="E38" t="s">
         <v>37</v>
@@ -2050,16 +2082,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>113</v>
+        <v>214</v>
       </c>
       <c r="B39" t="s">
-        <v>141</v>
+        <v>242</v>
       </c>
       <c r="C39" t="s">
-        <v>194</v>
+        <v>298</v>
       </c>
       <c r="D39" t="s">
-        <v>286</v>
+        <v>138</v>
       </c>
       <c r="E39" t="s">
         <v>38</v>
@@ -2067,16 +2099,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>214</v>
       </c>
       <c r="B40" t="s">
-        <v>141</v>
+        <v>242</v>
       </c>
       <c r="C40" t="s">
-        <v>195</v>
+        <v>299</v>
       </c>
       <c r="D40" t="s">
-        <v>287</v>
+        <v>139</v>
       </c>
       <c r="E40" t="s">
         <v>39</v>
@@ -2084,16 +2116,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>215</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>243</v>
       </c>
       <c r="C41" t="s">
-        <v>196</v>
+        <v>300</v>
       </c>
       <c r="D41" t="s">
-        <v>288</v>
+        <v>140</v>
       </c>
       <c r="E41" t="s">
         <v>40</v>
@@ -2101,16 +2133,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>215</v>
       </c>
       <c r="B42" t="s">
-        <v>143</v>
+        <v>244</v>
       </c>
       <c r="C42" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
       <c r="D42" t="s">
-        <v>289</v>
+        <v>141</v>
       </c>
       <c r="E42" t="s">
         <v>41</v>
@@ -2118,16 +2150,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>215</v>
       </c>
       <c r="B43" t="s">
-        <v>143</v>
+        <v>244</v>
       </c>
       <c r="C43" t="s">
-        <v>198</v>
+        <v>302</v>
       </c>
       <c r="D43" t="s">
-        <v>290</v>
+        <v>142</v>
       </c>
       <c r="E43" t="s">
         <v>42</v>
@@ -2135,16 +2167,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>114</v>
+        <v>215</v>
       </c>
       <c r="B44" t="s">
+        <v>244</v>
+      </c>
+      <c r="C44" t="s">
+        <v>303</v>
+      </c>
+      <c r="D44" t="s">
         <v>143</v>
-      </c>
-      <c r="C44" t="s">
-        <v>199</v>
-      </c>
-      <c r="D44" t="s">
-        <v>291</v>
       </c>
       <c r="E44" t="s">
         <v>43</v>
@@ -2152,16 +2184,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>114</v>
+        <v>215</v>
       </c>
       <c r="B45" t="s">
-        <v>143</v>
+        <v>244</v>
       </c>
       <c r="C45" t="s">
-        <v>200</v>
+        <v>304</v>
       </c>
       <c r="D45" t="s">
-        <v>292</v>
+        <v>144</v>
       </c>
       <c r="E45" t="s">
         <v>44</v>
@@ -2169,16 +2201,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>115</v>
+        <v>216</v>
       </c>
       <c r="B46" t="s">
-        <v>144</v>
+        <v>245</v>
       </c>
       <c r="C46" t="s">
-        <v>201</v>
+        <v>305</v>
       </c>
       <c r="D46" t="s">
-        <v>293</v>
+        <v>145</v>
       </c>
       <c r="E46" t="s">
         <v>45</v>
@@ -2186,16 +2218,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>115</v>
+        <v>216</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>245</v>
       </c>
       <c r="C47" t="s">
-        <v>202</v>
+        <v>306</v>
       </c>
       <c r="D47" t="s">
-        <v>294</v>
+        <v>146</v>
       </c>
       <c r="E47" t="s">
         <v>46</v>
@@ -2203,16 +2235,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>115</v>
+        <v>216</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>245</v>
       </c>
       <c r="C48" t="s">
-        <v>203</v>
+        <v>307</v>
       </c>
       <c r="D48" t="s">
-        <v>295</v>
+        <v>147</v>
       </c>
       <c r="E48" t="s">
         <v>47</v>
@@ -2220,16 +2252,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>115</v>
+        <v>216</v>
       </c>
       <c r="B49" t="s">
-        <v>144</v>
+        <v>245</v>
       </c>
       <c r="C49" t="s">
-        <v>204</v>
+        <v>308</v>
       </c>
       <c r="D49" t="s">
-        <v>296</v>
+        <v>148</v>
       </c>
       <c r="E49" t="s">
         <v>48</v>
@@ -2237,16 +2269,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>115</v>
+        <v>216</v>
       </c>
       <c r="B50" t="s">
-        <v>144</v>
+        <v>245</v>
       </c>
       <c r="C50" t="s">
-        <v>205</v>
+        <v>309</v>
       </c>
       <c r="D50" t="s">
-        <v>297</v>
+        <v>149</v>
       </c>
       <c r="E50" t="s">
         <v>49</v>
@@ -2254,16 +2286,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>115</v>
+        <v>216</v>
       </c>
       <c r="B51" t="s">
-        <v>144</v>
+        <v>245</v>
       </c>
       <c r="C51" t="s">
-        <v>206</v>
+        <v>310</v>
       </c>
       <c r="D51" t="s">
-        <v>298</v>
+        <v>150</v>
       </c>
       <c r="E51" t="s">
         <v>50</v>
@@ -2271,16 +2303,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>116</v>
+        <v>217</v>
       </c>
       <c r="B52" t="s">
-        <v>145</v>
+        <v>246</v>
       </c>
       <c r="C52" t="s">
-        <v>207</v>
+        <v>311</v>
       </c>
       <c r="D52" t="s">
-        <v>299</v>
+        <v>151</v>
       </c>
       <c r="E52" t="s">
         <v>51</v>
@@ -2288,16 +2320,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>116</v>
+        <v>217</v>
       </c>
       <c r="B53" t="s">
-        <v>145</v>
+        <v>246</v>
       </c>
       <c r="C53" t="s">
-        <v>208</v>
+        <v>312</v>
       </c>
       <c r="D53" t="s">
-        <v>300</v>
+        <v>152</v>
       </c>
       <c r="E53" t="s">
         <v>52</v>
@@ -2305,16 +2337,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>116</v>
+        <v>217</v>
       </c>
       <c r="B54" t="s">
-        <v>145</v>
+        <v>246</v>
       </c>
       <c r="C54" t="s">
-        <v>209</v>
+        <v>313</v>
       </c>
       <c r="D54" t="s">
-        <v>301</v>
+        <v>153</v>
       </c>
       <c r="E54" t="s">
         <v>53</v>
@@ -2322,16 +2354,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>117</v>
+        <v>218</v>
       </c>
       <c r="B55" t="s">
-        <v>146</v>
+        <v>247</v>
       </c>
       <c r="C55" t="s">
-        <v>210</v>
+        <v>314</v>
       </c>
       <c r="D55" t="s">
-        <v>302</v>
+        <v>154</v>
       </c>
       <c r="E55" t="s">
         <v>54</v>
@@ -2339,16 +2371,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>117</v>
+        <v>218</v>
       </c>
       <c r="B56" t="s">
-        <v>146</v>
+        <v>247</v>
       </c>
       <c r="C56" t="s">
-        <v>211</v>
+        <v>315</v>
       </c>
       <c r="D56" t="s">
-        <v>303</v>
+        <v>155</v>
       </c>
       <c r="E56" t="s">
         <v>55</v>
@@ -2356,16 +2388,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>117</v>
+        <v>218</v>
       </c>
       <c r="B57" t="s">
-        <v>147</v>
+        <v>248</v>
       </c>
       <c r="C57" t="s">
-        <v>212</v>
+        <v>316</v>
       </c>
       <c r="D57" t="s">
-        <v>304</v>
+        <v>156</v>
       </c>
       <c r="E57" t="s">
         <v>56</v>
@@ -2373,16 +2405,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>117</v>
+        <v>218</v>
       </c>
       <c r="B58" t="s">
-        <v>147</v>
+        <v>248</v>
       </c>
       <c r="C58" t="s">
-        <v>213</v>
+        <v>317</v>
       </c>
       <c r="D58" t="s">
-        <v>305</v>
+        <v>157</v>
       </c>
       <c r="E58" t="s">
         <v>57</v>
@@ -2390,16 +2422,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>118</v>
+        <v>219</v>
       </c>
       <c r="B59" t="s">
-        <v>148</v>
+        <v>249</v>
       </c>
       <c r="C59" t="s">
-        <v>214</v>
+        <v>318</v>
       </c>
       <c r="D59" t="s">
-        <v>306</v>
+        <v>158</v>
       </c>
       <c r="E59" t="s">
         <v>58</v>
@@ -2407,16 +2439,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>119</v>
+        <v>220</v>
       </c>
       <c r="B60" t="s">
-        <v>149</v>
+        <v>250</v>
       </c>
       <c r="C60" t="s">
-        <v>215</v>
+        <v>319</v>
       </c>
       <c r="D60" t="s">
-        <v>307</v>
+        <v>159</v>
       </c>
       <c r="E60" t="s">
         <v>59</v>
@@ -2424,16 +2456,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>119</v>
+        <v>220</v>
       </c>
       <c r="B61" t="s">
-        <v>149</v>
+        <v>250</v>
       </c>
       <c r="C61" t="s">
-        <v>215</v>
+        <v>320</v>
       </c>
       <c r="D61" t="s">
-        <v>308</v>
+        <v>160</v>
       </c>
       <c r="E61" t="s">
         <v>60</v>
@@ -2441,16 +2473,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>119</v>
+        <v>220</v>
       </c>
       <c r="B62" t="s">
-        <v>150</v>
+        <v>251</v>
       </c>
       <c r="C62" t="s">
-        <v>215</v>
+        <v>321</v>
       </c>
       <c r="D62" t="s">
-        <v>309</v>
+        <v>161</v>
       </c>
       <c r="E62" t="s">
         <v>61</v>
@@ -2458,16 +2490,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>119</v>
+        <v>220</v>
       </c>
       <c r="B63" t="s">
-        <v>150</v>
+        <v>251</v>
       </c>
       <c r="C63" t="s">
-        <v>215</v>
+        <v>322</v>
       </c>
       <c r="D63" t="s">
-        <v>310</v>
+        <v>162</v>
       </c>
       <c r="E63" t="s">
         <v>62</v>
@@ -2475,16 +2507,16 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>120</v>
+        <v>221</v>
       </c>
       <c r="B64" t="s">
-        <v>151</v>
+        <v>252</v>
       </c>
       <c r="C64" t="s">
-        <v>216</v>
+        <v>323</v>
       </c>
       <c r="D64" t="s">
-        <v>311</v>
+        <v>163</v>
       </c>
       <c r="E64" t="s">
         <v>63</v>
@@ -2492,16 +2524,16 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>120</v>
+        <v>221</v>
       </c>
       <c r="B65" t="s">
-        <v>151</v>
+        <v>252</v>
       </c>
       <c r="C65" t="s">
-        <v>217</v>
+        <v>324</v>
       </c>
       <c r="D65" t="s">
-        <v>312</v>
+        <v>164</v>
       </c>
       <c r="E65" t="s">
         <v>64</v>
@@ -2509,16 +2541,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>120</v>
+        <v>221</v>
       </c>
       <c r="B66" t="s">
-        <v>151</v>
+        <v>252</v>
       </c>
       <c r="C66" t="s">
-        <v>218</v>
+        <v>325</v>
       </c>
       <c r="D66" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
       <c r="E66" t="s">
         <v>65</v>
@@ -2526,16 +2558,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>120</v>
+        <v>221</v>
       </c>
       <c r="B67" t="s">
-        <v>151</v>
+        <v>252</v>
       </c>
       <c r="C67" t="s">
-        <v>219</v>
+        <v>326</v>
       </c>
       <c r="D67" t="s">
-        <v>314</v>
+        <v>166</v>
       </c>
       <c r="E67" t="s">
         <v>66</v>
@@ -2543,16 +2575,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>120</v>
+        <v>221</v>
       </c>
       <c r="B68" t="s">
-        <v>151</v>
+        <v>252</v>
       </c>
       <c r="C68" t="s">
-        <v>220</v>
+        <v>327</v>
       </c>
       <c r="D68" t="s">
-        <v>315</v>
+        <v>167</v>
       </c>
       <c r="E68" t="s">
         <v>67</v>
@@ -2560,16 +2592,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>120</v>
+        <v>221</v>
       </c>
       <c r="B69" t="s">
-        <v>151</v>
+        <v>252</v>
       </c>
       <c r="C69" t="s">
-        <v>221</v>
+        <v>328</v>
       </c>
       <c r="D69" t="s">
-        <v>316</v>
+        <v>168</v>
       </c>
       <c r="E69" t="s">
         <v>68</v>
@@ -2577,16 +2609,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>221</v>
       </c>
       <c r="B70" t="s">
-        <v>151</v>
+        <v>252</v>
       </c>
       <c r="C70" t="s">
-        <v>222</v>
+        <v>329</v>
       </c>
       <c r="D70" t="s">
-        <v>317</v>
+        <v>169</v>
       </c>
       <c r="E70" t="s">
         <v>69</v>
@@ -2594,16 +2626,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>120</v>
+        <v>221</v>
       </c>
       <c r="B71" t="s">
-        <v>151</v>
+        <v>252</v>
       </c>
       <c r="C71" t="s">
-        <v>223</v>
+        <v>330</v>
       </c>
       <c r="D71" t="s">
-        <v>318</v>
+        <v>170</v>
       </c>
       <c r="E71" t="s">
         <v>70</v>
@@ -2611,16 +2643,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="B72" t="s">
-        <v>152</v>
+        <v>253</v>
       </c>
       <c r="C72" t="s">
-        <v>224</v>
+        <v>331</v>
       </c>
       <c r="D72" t="s">
-        <v>319</v>
+        <v>171</v>
       </c>
       <c r="E72" t="s">
         <v>71</v>
@@ -2628,16 +2660,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="B73" t="s">
-        <v>152</v>
+        <v>253</v>
       </c>
       <c r="C73" t="s">
-        <v>225</v>
+        <v>332</v>
       </c>
       <c r="D73" t="s">
-        <v>320</v>
+        <v>172</v>
       </c>
       <c r="E73" t="s">
         <v>72</v>
@@ -2645,16 +2677,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="B74" t="s">
-        <v>152</v>
+        <v>253</v>
       </c>
       <c r="C74" t="s">
-        <v>226</v>
+        <v>333</v>
       </c>
       <c r="D74" t="s">
-        <v>321</v>
+        <v>173</v>
       </c>
       <c r="E74" t="s">
         <v>73</v>
@@ -2662,16 +2694,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="B75" t="s">
-        <v>152</v>
+        <v>253</v>
       </c>
       <c r="C75" t="s">
-        <v>227</v>
+        <v>334</v>
       </c>
       <c r="D75" t="s">
-        <v>322</v>
+        <v>174</v>
       </c>
       <c r="E75" t="s">
         <v>74</v>
@@ -2679,16 +2711,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="B76" t="s">
-        <v>152</v>
+        <v>253</v>
       </c>
       <c r="C76" t="s">
-        <v>228</v>
+        <v>335</v>
       </c>
       <c r="D76" t="s">
-        <v>323</v>
+        <v>175</v>
       </c>
       <c r="E76" t="s">
         <v>75</v>
@@ -2696,16 +2728,16 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="B77" t="s">
-        <v>152</v>
+        <v>253</v>
       </c>
       <c r="C77" t="s">
-        <v>229</v>
+        <v>336</v>
       </c>
       <c r="D77" t="s">
-        <v>324</v>
+        <v>176</v>
       </c>
       <c r="E77" t="s">
         <v>76</v>
@@ -2713,16 +2745,16 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="B78" t="s">
-        <v>152</v>
+        <v>253</v>
       </c>
       <c r="C78" t="s">
-        <v>230</v>
+        <v>337</v>
       </c>
       <c r="D78" t="s">
-        <v>325</v>
+        <v>177</v>
       </c>
       <c r="E78" t="s">
         <v>77</v>
@@ -2730,16 +2762,16 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="B79" t="s">
-        <v>152</v>
+        <v>253</v>
       </c>
       <c r="C79" t="s">
-        <v>230</v>
+        <v>338</v>
       </c>
       <c r="D79" t="s">
-        <v>326</v>
+        <v>178</v>
       </c>
       <c r="E79" t="s">
         <v>78</v>
@@ -2747,16 +2779,16 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="B80" t="s">
-        <v>153</v>
+        <v>254</v>
       </c>
       <c r="C80" t="s">
-        <v>231</v>
+        <v>339</v>
       </c>
       <c r="D80" t="s">
-        <v>327</v>
+        <v>179</v>
       </c>
       <c r="E80" t="s">
         <v>79</v>
@@ -2764,16 +2796,16 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="B81" t="s">
-        <v>153</v>
+        <v>254</v>
       </c>
       <c r="C81" t="s">
-        <v>232</v>
+        <v>340</v>
       </c>
       <c r="D81" t="s">
-        <v>328</v>
+        <v>180</v>
       </c>
       <c r="E81" t="s">
         <v>80</v>
@@ -2781,16 +2813,16 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="B82" t="s">
-        <v>153</v>
+        <v>254</v>
       </c>
       <c r="C82" t="s">
-        <v>233</v>
+        <v>341</v>
       </c>
       <c r="D82" t="s">
-        <v>329</v>
+        <v>181</v>
       </c>
       <c r="E82" t="s">
         <v>81</v>
@@ -2798,16 +2830,16 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="B83" t="s">
-        <v>153</v>
+        <v>254</v>
       </c>
       <c r="C83" t="s">
-        <v>234</v>
+        <v>342</v>
       </c>
       <c r="D83" t="s">
-        <v>330</v>
+        <v>182</v>
       </c>
       <c r="E83" t="s">
         <v>82</v>
@@ -2815,16 +2847,16 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>121</v>
+        <v>222</v>
       </c>
       <c r="B84" t="s">
-        <v>153</v>
+        <v>254</v>
       </c>
       <c r="C84" t="s">
-        <v>234</v>
+        <v>343</v>
       </c>
       <c r="D84" t="s">
-        <v>331</v>
+        <v>183</v>
       </c>
       <c r="E84" t="s">
         <v>83</v>
@@ -2832,16 +2864,16 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>122</v>
+        <v>223</v>
       </c>
       <c r="B85" t="s">
-        <v>154</v>
+        <v>255</v>
       </c>
       <c r="C85" t="s">
-        <v>235</v>
+        <v>344</v>
       </c>
       <c r="D85" t="s">
-        <v>332</v>
+        <v>184</v>
       </c>
       <c r="E85" t="s">
         <v>84</v>
@@ -2849,16 +2881,16 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>122</v>
+        <v>223</v>
       </c>
       <c r="B86" t="s">
-        <v>154</v>
+        <v>255</v>
       </c>
       <c r="C86" t="s">
-        <v>236</v>
+        <v>345</v>
       </c>
       <c r="D86" t="s">
-        <v>333</v>
+        <v>185</v>
       </c>
       <c r="E86" t="s">
         <v>85</v>
@@ -2866,16 +2898,16 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>122</v>
+        <v>223</v>
       </c>
       <c r="B87" t="s">
-        <v>154</v>
+        <v>255</v>
       </c>
       <c r="C87" t="s">
-        <v>237</v>
+        <v>346</v>
       </c>
       <c r="D87" t="s">
-        <v>334</v>
+        <v>186</v>
       </c>
       <c r="E87" t="s">
         <v>86</v>
@@ -2883,16 +2915,16 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>122</v>
+        <v>223</v>
       </c>
       <c r="B88" t="s">
-        <v>154</v>
+        <v>255</v>
       </c>
       <c r="C88" t="s">
-        <v>238</v>
+        <v>347</v>
       </c>
       <c r="D88" t="s">
-        <v>335</v>
+        <v>187</v>
       </c>
       <c r="E88" t="s">
         <v>87</v>
@@ -2900,16 +2932,16 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>123</v>
+        <v>224</v>
       </c>
       <c r="B89" t="s">
-        <v>155</v>
+        <v>256</v>
       </c>
       <c r="C89" t="s">
-        <v>239</v>
+        <v>348</v>
       </c>
       <c r="D89" t="s">
-        <v>336</v>
+        <v>188</v>
       </c>
       <c r="E89" t="s">
         <v>88</v>
@@ -2917,16 +2949,16 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>123</v>
+        <v>224</v>
       </c>
       <c r="B90" t="s">
-        <v>155</v>
+        <v>256</v>
       </c>
       <c r="C90" t="s">
-        <v>240</v>
+        <v>349</v>
       </c>
       <c r="D90" t="s">
-        <v>337</v>
+        <v>189</v>
       </c>
       <c r="E90" t="s">
         <v>89</v>
@@ -2934,16 +2966,16 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>123</v>
+        <v>224</v>
       </c>
       <c r="B91" t="s">
-        <v>155</v>
+        <v>256</v>
       </c>
       <c r="C91" t="s">
-        <v>241</v>
+        <v>350</v>
       </c>
       <c r="D91" t="s">
-        <v>338</v>
+        <v>190</v>
       </c>
       <c r="E91" t="s">
         <v>90</v>
@@ -2951,16 +2983,16 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>124</v>
+        <v>225</v>
       </c>
       <c r="B92" t="s">
-        <v>156</v>
+        <v>257</v>
       </c>
       <c r="C92" t="s">
-        <v>241</v>
+        <v>351</v>
       </c>
       <c r="D92" t="s">
-        <v>339</v>
+        <v>191</v>
       </c>
       <c r="E92" t="s">
         <v>91</v>
@@ -2968,16 +3000,16 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>125</v>
+        <v>226</v>
       </c>
       <c r="B93" t="s">
-        <v>157</v>
+        <v>258</v>
       </c>
       <c r="C93" t="s">
-        <v>241</v>
+        <v>352</v>
       </c>
       <c r="D93" t="s">
-        <v>340</v>
+        <v>192</v>
       </c>
       <c r="E93" t="s">
         <v>92</v>
@@ -2985,16 +3017,16 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="B94" t="s">
-        <v>158</v>
+        <v>259</v>
       </c>
       <c r="C94" t="s">
-        <v>242</v>
+        <v>353</v>
       </c>
       <c r="D94" t="s">
-        <v>341</v>
+        <v>193</v>
       </c>
       <c r="E94" t="s">
         <v>93</v>
@@ -3002,16 +3034,16 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="B95" t="s">
-        <v>158</v>
+        <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>242</v>
+        <v>354</v>
       </c>
       <c r="D95" t="s">
-        <v>342</v>
+        <v>194</v>
       </c>
       <c r="E95" t="s">
         <v>94</v>
@@ -3019,16 +3051,16 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="B96" t="s">
-        <v>158</v>
+        <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>243</v>
+        <v>355</v>
       </c>
       <c r="D96" t="s">
-        <v>343</v>
+        <v>195</v>
       </c>
       <c r="E96" t="s">
         <v>95</v>
@@ -3036,16 +3068,16 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="B97" t="s">
-        <v>158</v>
+        <v>259</v>
       </c>
       <c r="C97" t="s">
-        <v>244</v>
+        <v>356</v>
       </c>
       <c r="D97" t="s">
-        <v>344</v>
+        <v>196</v>
       </c>
       <c r="E97" t="s">
         <v>96</v>
@@ -3053,16 +3085,16 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="B98" t="s">
-        <v>158</v>
+        <v>259</v>
       </c>
       <c r="C98" t="s">
-        <v>245</v>
+        <v>357</v>
       </c>
       <c r="D98" t="s">
-        <v>345</v>
+        <v>197</v>
       </c>
       <c r="E98" t="s">
         <v>97</v>
@@ -3070,16 +3102,16 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="B99" t="s">
-        <v>158</v>
+        <v>259</v>
       </c>
       <c r="C99" t="s">
-        <v>246</v>
+        <v>358</v>
       </c>
       <c r="D99" t="s">
-        <v>346</v>
+        <v>198</v>
       </c>
       <c r="E99" t="s">
         <v>98</v>
@@ -3087,16 +3119,16 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>126</v>
+        <v>227</v>
       </c>
       <c r="B100" t="s">
-        <v>158</v>
+        <v>259</v>
       </c>
       <c r="C100" t="s">
-        <v>247</v>
+        <v>359</v>
       </c>
       <c r="D100" t="s">
-        <v>347</v>
+        <v>199</v>
       </c>
       <c r="E100" t="s">
         <v>99</v>
@@ -3105,6 +3137,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>